--- a/pages/WR_progressions/Womens_Madison.xlsx
+++ b/pages/WR_progressions/Womens_Madison.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\WR_progressions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC4DA308-690C-4D1B-A425-477DA20B506B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C0CF36B-ACE3-4F2C-975A-A570E04A121D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{8F2B8F41-998D-4BB8-BE11-A97939F5BC1E}"/>
   </bookViews>
@@ -457,17 +457,10 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -596,12 +589,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
@@ -609,26 +601,25 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="4" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="4" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -639,11 +630,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="17">
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -699,6 +685,11 @@
           <bgColor theme="9" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
     </dxf>
     <dxf>
       <fill>
@@ -1143,131 +1134,143 @@
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="B2" s="20">
+      <c r="B2" s="18">
         <v>2025</v>
       </c>
       <c r="C2" s="2">
         <v>45952</v>
       </c>
-      <c r="D2" s="20" t="s">
+      <c r="D2" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="G2" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="H2" s="25">
+      <c r="H2" s="23">
         <v>22.484931506849314</v>
       </c>
-      <c r="I2" s="25">
+      <c r="I2" s="23">
         <v>31.635616438356163</v>
       </c>
-      <c r="J2" s="24">
+      <c r="J2" s="22">
         <v>1</v>
       </c>
-      <c r="K2" s="20">
-        <v>0</v>
-      </c>
-      <c r="L2" s="20"/>
-      <c r="M2" s="20"/>
-      <c r="N2" s="20">
+      <c r="K2" s="18">
+        <v>0</v>
+      </c>
+      <c r="L2" s="18">
+        <v>8</v>
+      </c>
+      <c r="M2" s="18">
+        <v>2</v>
+      </c>
+      <c r="N2" s="18">
         <v>30</v>
       </c>
-      <c r="O2" s="20">
+      <c r="O2" s="18">
         <v>54.573</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="B3" s="20">
+      <c r="B3" s="18">
         <v>2025</v>
       </c>
       <c r="C3" s="2">
         <v>45952</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="D3" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="H3" s="25">
+      <c r="H3" s="23">
         <v>25.2</v>
       </c>
-      <c r="I3" s="25">
+      <c r="I3" s="23">
         <v>27.92876712328767</v>
       </c>
-      <c r="J3" s="24">
+      <c r="J3" s="22">
         <v>2</v>
       </c>
-      <c r="K3" s="20">
-        <v>0</v>
-      </c>
-      <c r="L3" s="20"/>
-      <c r="M3" s="20"/>
-      <c r="N3" s="20">
+      <c r="K3" s="18">
+        <v>0</v>
+      </c>
+      <c r="L3" s="18">
+        <v>8</v>
+      </c>
+      <c r="M3" s="18">
+        <v>3</v>
+      </c>
+      <c r="N3" s="18">
         <v>24</v>
       </c>
-      <c r="O3" s="20">
+      <c r="O3" s="18">
         <v>54.573</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="B4" s="20">
+      <c r="B4" s="18">
         <v>2025</v>
       </c>
       <c r="C4" s="2">
         <v>45952</v>
       </c>
-      <c r="D4" s="20" t="s">
+      <c r="D4" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="G4" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="H4" s="25">
+      <c r="H4" s="23">
         <v>26.347945205479451</v>
       </c>
-      <c r="I4" s="25">
+      <c r="I4" s="23">
         <v>24.838356164383562</v>
       </c>
-      <c r="J4" s="24">
-        <v>3</v>
-      </c>
-      <c r="K4" s="20">
-        <v>0</v>
-      </c>
-      <c r="L4" s="20"/>
-      <c r="M4" s="20"/>
-      <c r="N4" s="20">
+      <c r="J4" s="22">
+        <v>3</v>
+      </c>
+      <c r="K4" s="18">
+        <v>0</v>
+      </c>
+      <c r="L4" s="18">
+        <v>7</v>
+      </c>
+      <c r="M4" s="18">
+        <v>1</v>
+      </c>
+      <c r="N4" s="18">
         <v>20</v>
       </c>
-      <c r="O4" s="20">
+      <c r="O4" s="18">
         <v>54.573</v>
       </c>
     </row>
@@ -1284,13 +1287,13 @@
       <c r="D5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="F5" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G5" s="8" t="s">
+      <c r="G5" s="7" t="s">
         <v>20</v>
       </c>
       <c r="H5" s="3">
@@ -1299,16 +1302,22 @@
       <c r="I5" s="3">
         <v>24.216438356164385</v>
       </c>
-      <c r="J5" s="24">
+      <c r="J5" s="22">
         <v>1</v>
       </c>
       <c r="K5">
         <v>20</v>
       </c>
+      <c r="L5">
+        <v>9</v>
+      </c>
+      <c r="M5">
+        <v>4</v>
+      </c>
       <c r="N5">
         <v>53</v>
       </c>
-      <c r="O5" s="5">
+      <c r="O5" s="4">
         <v>54.107999999999997</v>
       </c>
     </row>
@@ -1325,13 +1334,13 @@
       <c r="D6" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="G6" s="7" t="s">
         <v>19</v>
       </c>
       <c r="H6" s="3">
@@ -1340,16 +1349,22 @@
       <c r="I6" s="3">
         <v>25.717808219178082</v>
       </c>
-      <c r="J6" s="24">
+      <c r="J6" s="22">
         <v>2</v>
       </c>
       <c r="K6">
         <v>20</v>
       </c>
+      <c r="L6">
+        <v>8</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
       <c r="N6">
         <v>43</v>
       </c>
-      <c r="O6" s="5">
+      <c r="O6" s="4">
         <v>54.107999999999997</v>
       </c>
     </row>
@@ -1366,13 +1381,13 @@
       <c r="D7" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="F7" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="G7" s="7" t="s">
         <v>26</v>
       </c>
       <c r="H7" s="3">
@@ -1381,16 +1396,22 @@
       <c r="I7" s="3">
         <v>26.07123287671233</v>
       </c>
-      <c r="J7" s="24">
+      <c r="J7" s="22">
         <v>3</v>
       </c>
       <c r="K7">
         <v>20</v>
       </c>
+      <c r="L7">
+        <v>7</v>
+      </c>
+      <c r="M7">
+        <v>3</v>
+      </c>
       <c r="N7">
         <v>43</v>
       </c>
-      <c r="O7" s="5">
+      <c r="O7" s="4">
         <v>54.107999999999997</v>
       </c>
     </row>
@@ -1407,13 +1428,13 @@
       <c r="D8" t="s">
         <v>18</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="E8" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="F8" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="G8" s="8" t="s">
+      <c r="G8" s="7" t="s">
         <v>20</v>
       </c>
       <c r="H8" s="3">
@@ -1422,11 +1443,17 @@
       <c r="I8" s="3">
         <v>32.290410958904111</v>
       </c>
-      <c r="J8" s="24">
+      <c r="J8" s="22">
         <v>1</v>
       </c>
       <c r="K8">
         <v>20</v>
+      </c>
+      <c r="L8">
+        <v>9</v>
+      </c>
+      <c r="M8">
+        <v>3</v>
       </c>
       <c r="N8">
         <v>46</v>
@@ -1448,13 +1475,13 @@
       <c r="D9" t="s">
         <v>18</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="F9" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="7" t="s">
         <v>30</v>
       </c>
       <c r="H9" s="3">
@@ -1463,11 +1490,17 @@
       <c r="I9" s="3">
         <v>26.920547945205481</v>
       </c>
-      <c r="J9" s="24">
+      <c r="J9" s="22">
         <v>2</v>
       </c>
       <c r="K9">
         <v>20</v>
+      </c>
+      <c r="L9">
+        <v>8</v>
+      </c>
+      <c r="M9">
+        <v>1</v>
       </c>
       <c r="N9">
         <v>43</v>
@@ -1489,13 +1522,13 @@
       <c r="D10" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="E10" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="F10" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="G10" s="8" t="s">
+      <c r="G10" s="7" t="s">
         <v>28</v>
       </c>
       <c r="H10" s="3">
@@ -1504,11 +1537,17 @@
       <c r="I10" s="3">
         <v>30.627397260273973</v>
       </c>
-      <c r="J10" s="24">
+      <c r="J10" s="22">
         <v>3</v>
       </c>
       <c r="K10">
         <v>0</v>
+      </c>
+      <c r="L10">
+        <v>10</v>
+      </c>
+      <c r="M10">
+        <v>5</v>
       </c>
       <c r="N10">
         <v>42</v>
@@ -1530,13 +1569,13 @@
       <c r="D11" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="E11" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="F11" s="8" t="s">
+      <c r="F11" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="G11" s="8" t="s">
+      <c r="G11" s="7" t="s">
         <v>23</v>
       </c>
       <c r="H11" s="3">
@@ -1545,11 +1584,17 @@
       <c r="I11" s="3">
         <v>23.717808219178082</v>
       </c>
-      <c r="J11" s="24">
+      <c r="J11" s="22">
         <v>1</v>
       </c>
       <c r="K11">
         <v>20</v>
+      </c>
+      <c r="L11">
+        <v>4</v>
+      </c>
+      <c r="M11">
+        <v>3</v>
       </c>
       <c r="N11">
         <v>37</v>
@@ -1571,13 +1616,13 @@
       <c r="D12" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="E12" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="F12" s="8" t="s">
+      <c r="F12" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="G12" s="8" t="s">
+      <c r="G12" s="7" t="s">
         <v>28</v>
       </c>
       <c r="H12" s="3">
@@ -1586,11 +1631,17 @@
       <c r="I12" s="3">
         <v>34.128767123287673</v>
       </c>
-      <c r="J12" s="24">
+      <c r="J12" s="22">
         <v>2</v>
       </c>
       <c r="K12">
         <v>0</v>
+      </c>
+      <c r="L12">
+        <v>8</v>
+      </c>
+      <c r="M12">
+        <v>3</v>
       </c>
       <c r="N12">
         <v>31</v>
@@ -1612,13 +1663,13 @@
       <c r="D13" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="E13" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="F13" s="8" t="s">
+      <c r="F13" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="G13" s="8" t="s">
+      <c r="G13" s="7" t="s">
         <v>15</v>
       </c>
       <c r="H13" s="3">
@@ -1627,11 +1678,17 @@
       <c r="I13" s="3">
         <v>20.621917808219177</v>
       </c>
-      <c r="J13" s="24">
+      <c r="J13" s="22">
         <v>3</v>
       </c>
       <c r="K13">
         <v>20</v>
+      </c>
+      <c r="L13">
+        <v>3</v>
+      </c>
+      <c r="M13">
+        <v>1</v>
       </c>
       <c r="N13">
         <v>28</v>
@@ -1653,13 +1710,13 @@
       <c r="D14" t="s">
         <v>14</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="E14" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="F14" s="8" t="s">
+      <c r="F14" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="G14" s="8" t="s">
+      <c r="G14" s="7" t="s">
         <v>28</v>
       </c>
       <c r="H14" s="3">
@@ -1668,11 +1725,17 @@
       <c r="I14" s="3">
         <v>33.723287671232875</v>
       </c>
-      <c r="J14" s="8">
+      <c r="J14" s="7">
         <v>1</v>
       </c>
       <c r="K14">
         <v>0</v>
+      </c>
+      <c r="L14">
+        <v>9</v>
+      </c>
+      <c r="M14">
+        <v>5</v>
       </c>
       <c r="N14">
         <v>37</v>
@@ -1694,13 +1757,13 @@
       <c r="D15" t="s">
         <v>14</v>
       </c>
-      <c r="E15" s="8" t="s">
+      <c r="E15" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="F15" s="8" t="s">
+      <c r="F15" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="G15" s="8" t="s">
+      <c r="G15" s="7" t="s">
         <v>30</v>
       </c>
       <c r="H15" s="3">
@@ -1709,11 +1772,17 @@
       <c r="I15" s="3">
         <v>26.402739726027399</v>
       </c>
-      <c r="J15" s="8">
+      <c r="J15" s="7">
         <v>2</v>
       </c>
       <c r="K15">
         <v>0</v>
+      </c>
+      <c r="L15">
+        <v>7</v>
+      </c>
+      <c r="M15">
+        <v>2</v>
       </c>
       <c r="N15">
         <v>25</v>
@@ -1735,13 +1804,13 @@
       <c r="D16" t="s">
         <v>14</v>
       </c>
-      <c r="E16" s="8" t="s">
+      <c r="E16" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="F16" s="8" t="s">
+      <c r="F16" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="G16" s="8" t="s">
+      <c r="G16" s="7" t="s">
         <v>69</v>
       </c>
       <c r="H16" s="3">
@@ -1750,11 +1819,17 @@
       <c r="I16" s="3">
         <v>29.824657534246576</v>
       </c>
-      <c r="J16" s="8">
+      <c r="J16" s="7">
         <v>3</v>
       </c>
       <c r="K16">
         <v>0</v>
+      </c>
+      <c r="L16">
+        <v>6</v>
+      </c>
+      <c r="M16">
+        <v>2</v>
       </c>
       <c r="N16">
         <v>19</v>
@@ -1776,13 +1851,13 @@
       <c r="D17" t="s">
         <v>14</v>
       </c>
-      <c r="E17" s="8" t="s">
+      <c r="E17" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="F17" s="8" t="s">
+      <c r="F17" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="G17" s="8" t="s">
+      <c r="G17" s="7" t="s">
         <v>72</v>
       </c>
       <c r="H17" s="3">
@@ -1791,11 +1866,17 @@
       <c r="I17" s="3">
         <v>22.186301369863013</v>
       </c>
-      <c r="J17" s="8">
+      <c r="J17" s="7">
         <v>1</v>
       </c>
       <c r="K17">
         <v>20</v>
+      </c>
+      <c r="L17">
+        <v>7</v>
+      </c>
+      <c r="M17">
+        <v>4</v>
       </c>
       <c r="N17">
         <v>54</v>
@@ -1817,13 +1898,13 @@
       <c r="D18" t="s">
         <v>14</v>
       </c>
-      <c r="E18" s="8" t="s">
+      <c r="E18" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="F18" s="8" t="s">
+      <c r="F18" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G18" s="8" t="s">
+      <c r="G18" s="7" t="s">
         <v>26</v>
       </c>
       <c r="H18" s="3">
@@ -1832,11 +1913,17 @@
       <c r="I18" s="3">
         <v>25.076712328767123</v>
       </c>
-      <c r="J18" s="8">
+      <c r="J18" s="7">
         <v>2</v>
       </c>
       <c r="K18">
         <v>20</v>
+      </c>
+      <c r="L18">
+        <v>10</v>
+      </c>
+      <c r="M18">
+        <v>4</v>
       </c>
       <c r="N18">
         <v>53</v>
@@ -1858,13 +1945,13 @@
       <c r="D19" t="s">
         <v>14</v>
       </c>
-      <c r="E19" s="8" t="s">
+      <c r="E19" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="F19" s="8" t="s">
+      <c r="F19" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="G19" s="8" t="s">
+      <c r="G19" s="7" t="s">
         <v>15</v>
       </c>
       <c r="H19" s="3">
@@ -1873,11 +1960,17 @@
       <c r="I19" s="3">
         <v>20.139726027397259</v>
       </c>
-      <c r="J19" s="8">
+      <c r="J19" s="7">
         <v>3</v>
       </c>
       <c r="K19">
         <v>20</v>
+      </c>
+      <c r="L19">
+        <v>7</v>
+      </c>
+      <c r="M19">
+        <v>3</v>
       </c>
       <c r="N19">
         <v>49</v>
@@ -1899,13 +1992,13 @@
       <c r="D20" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E20" s="8" t="s">
+      <c r="E20" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="F20" s="8" t="s">
+      <c r="F20" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="G20" s="8" t="s">
+      <c r="G20" s="7" t="s">
         <v>28</v>
       </c>
       <c r="H20" s="3">
@@ -1914,11 +2007,17 @@
       <c r="I20" s="3">
         <v>29.427397260273974</v>
       </c>
-      <c r="J20" s="24">
+      <c r="J20" s="22">
         <v>1</v>
       </c>
       <c r="K20">
         <v>0</v>
+      </c>
+      <c r="L20">
+        <v>7</v>
+      </c>
+      <c r="M20">
+        <v>5</v>
       </c>
       <c r="N20">
         <v>31</v>
@@ -1940,13 +2039,13 @@
       <c r="D21" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E21" s="8" t="s">
+      <c r="E21" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="F21" s="8" t="s">
+      <c r="F21" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="G21" s="8" t="s">
+      <c r="G21" s="7" t="s">
         <v>42</v>
       </c>
       <c r="H21" s="3">
@@ -1955,11 +2054,17 @@
       <c r="I21" s="3">
         <v>27.950684931506849</v>
       </c>
-      <c r="J21" s="24">
+      <c r="J21" s="22">
         <v>2</v>
       </c>
       <c r="K21">
         <v>0</v>
+      </c>
+      <c r="L21">
+        <v>8</v>
+      </c>
+      <c r="M21">
+        <v>1</v>
       </c>
       <c r="N21">
         <v>27</v>
@@ -1981,13 +2086,13 @@
       <c r="D22" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E22" s="8" t="s">
+      <c r="E22" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="F22" s="8" t="s">
+      <c r="F22" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="G22" s="8" t="s">
+      <c r="G22" s="7" t="s">
         <v>69</v>
       </c>
       <c r="H22" s="3">
@@ -1996,11 +2101,17 @@
       <c r="I22" s="3">
         <v>29.632876712328766</v>
       </c>
-      <c r="J22" s="24">
+      <c r="J22" s="22">
         <v>3</v>
       </c>
       <c r="K22">
         <v>0</v>
+      </c>
+      <c r="L22">
+        <v>8</v>
+      </c>
+      <c r="M22">
+        <v>2</v>
       </c>
       <c r="N22">
         <v>23</v>
@@ -2010,25 +2121,25 @@
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A23" s="16" t="s">
+      <c r="A23" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="B23" s="17">
+      <c r="B23" s="15">
         <v>2023</v>
       </c>
       <c r="C23" s="2">
         <v>45146</v>
       </c>
-      <c r="D23" s="19" t="s">
+      <c r="D23" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="E23" s="8" t="s" cm="1">
+      <c r="E23" s="7" t="s" cm="1">
         <v>62</v>
       </c>
-      <c r="F23" s="8" t="s">
+      <c r="F23" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="G23" s="8" t="s">
+      <c r="G23" s="7" t="s">
         <v>28</v>
       </c>
       <c r="H23" s="3">
@@ -2037,11 +2148,17 @@
       <c r="I23" s="3">
         <v>28.926027397260274</v>
       </c>
-      <c r="J23" s="24">
+      <c r="J23" s="22">
         <v>1</v>
       </c>
-      <c r="K23" s="4">
-        <v>0</v>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>10</v>
+      </c>
+      <c r="M23">
+        <v>3</v>
       </c>
       <c r="N23">
         <v>28</v>
@@ -2051,25 +2168,25 @@
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A24" s="16" t="s">
+      <c r="A24" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="B24" s="17">
+      <c r="B24" s="15">
         <v>2023</v>
       </c>
       <c r="C24" s="2">
         <v>45146</v>
       </c>
-      <c r="D24" s="19" t="s">
+      <c r="D24" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="E24" s="8" t="s" cm="1">
+      <c r="E24" s="7" t="s" cm="1">
         <v>76</v>
       </c>
-      <c r="F24" s="8" t="s">
+      <c r="F24" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="G24" s="8" t="s">
+      <c r="G24" s="7" t="s">
         <v>42</v>
       </c>
       <c r="H24" s="3">
@@ -2078,11 +2195,17 @@
       <c r="I24" s="3">
         <v>27.449315068493149</v>
       </c>
-      <c r="J24" s="24">
+      <c r="J24" s="22">
         <v>2</v>
       </c>
-      <c r="K24" s="4">
-        <v>0</v>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>7</v>
+      </c>
+      <c r="M24">
+        <v>1</v>
       </c>
       <c r="N24">
         <v>25</v>
@@ -2092,25 +2215,25 @@
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A25" s="16" t="s">
+      <c r="A25" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="B25" s="17">
+      <c r="B25" s="15">
         <v>2023</v>
       </c>
       <c r="C25" s="2">
         <v>45146</v>
       </c>
-      <c r="D25" s="19" t="s">
+      <c r="D25" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="E25" s="8" t="s" cm="1">
+      <c r="E25" s="7" t="s" cm="1">
         <v>51</v>
       </c>
-      <c r="F25" s="8" t="s">
+      <c r="F25" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="G25" s="8" t="s">
+      <c r="G25" s="7" t="s">
         <v>30</v>
       </c>
       <c r="H25" s="3">
@@ -2119,11 +2242,17 @@
       <c r="I25" s="3">
         <v>24.575342465753426</v>
       </c>
-      <c r="J25" s="24">
-        <v>3</v>
-      </c>
-      <c r="K25" s="4">
-        <v>0</v>
+      <c r="J25" s="22">
+        <v>3</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>6</v>
+      </c>
+      <c r="M25">
+        <v>2</v>
       </c>
       <c r="N25">
         <v>22</v>
@@ -2145,13 +2274,13 @@
       <c r="D26" t="s">
         <v>14</v>
       </c>
-      <c r="E26" s="8" t="s">
+      <c r="E26" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="F26" s="8" t="s">
+      <c r="F26" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="G26" s="8" t="s">
+      <c r="G26" s="7" t="s">
         <v>16</v>
       </c>
       <c r="H26" s="3">
@@ -2160,11 +2289,17 @@
       <c r="I26" s="3">
         <v>27.463013698630139</v>
       </c>
-      <c r="J26" s="24">
+      <c r="J26" s="22">
         <v>1</v>
       </c>
       <c r="K26">
         <v>20</v>
+      </c>
+      <c r="L26">
+        <v>9</v>
+      </c>
+      <c r="M26">
+        <v>3</v>
       </c>
       <c r="N26">
         <v>53</v>
@@ -2186,13 +2321,13 @@
       <c r="D27" t="s">
         <v>14</v>
       </c>
-      <c r="E27" s="8" t="s">
+      <c r="E27" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="F27" s="8" t="s">
+      <c r="F27" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="G27" s="8" t="s">
+      <c r="G27" s="7" t="s">
         <v>28</v>
       </c>
       <c r="H27" s="3">
@@ -2201,11 +2336,17 @@
       <c r="I27" s="3">
         <v>32.742465753424661</v>
       </c>
-      <c r="J27" s="24">
+      <c r="J27" s="22">
         <v>2</v>
       </c>
       <c r="K27">
         <v>20</v>
+      </c>
+      <c r="L27">
+        <v>8</v>
+      </c>
+      <c r="M27">
+        <v>2</v>
       </c>
       <c r="N27">
         <v>44</v>
@@ -2227,13 +2368,13 @@
       <c r="D28" t="s">
         <v>14</v>
       </c>
-      <c r="E28" s="8" t="s">
+      <c r="E28" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="F28" s="8" t="s">
+      <c r="F28" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="G28" s="8" t="s">
+      <c r="G28" s="7" t="s">
         <v>23</v>
       </c>
       <c r="H28" s="3">
@@ -2242,11 +2383,17 @@
       <c r="I28" s="3">
         <v>23.473972602739725</v>
       </c>
-      <c r="J28" s="24">
+      <c r="J28" s="22">
         <v>3</v>
       </c>
       <c r="K28">
         <v>20</v>
+      </c>
+      <c r="L28">
+        <v>6</v>
+      </c>
+      <c r="M28">
+        <v>3</v>
       </c>
       <c r="N28">
         <v>41</v>
@@ -2262,19 +2409,19 @@
       <c r="B29" s="1">
         <v>2023</v>
       </c>
-      <c r="C29" s="18">
+      <c r="C29" s="16">
         <v>45002</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E29" s="13" t="s">
+      <c r="E29" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="F29" s="13" t="s">
+      <c r="F29" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="G29" s="13" t="s">
+      <c r="G29" s="11" t="s">
         <v>30</v>
       </c>
       <c r="H29" s="3">
@@ -2283,16 +2430,22 @@
       <c r="I29" s="3">
         <v>23.906849315068492</v>
       </c>
-      <c r="J29" s="13">
+      <c r="J29" s="11">
         <v>1</v>
       </c>
-      <c r="K29" s="4">
-        <v>0</v>
+      <c r="K29">
+        <v>0</v>
+      </c>
+      <c r="L29">
+        <v>10</v>
+      </c>
+      <c r="M29">
+        <v>4</v>
       </c>
       <c r="N29">
         <v>35</v>
       </c>
-      <c r="O29" s="7">
+      <c r="O29" s="6">
         <v>50.966999999999999</v>
       </c>
     </row>
@@ -2303,19 +2456,19 @@
       <c r="B30" s="1">
         <v>2023</v>
       </c>
-      <c r="C30" s="18">
+      <c r="C30" s="16">
         <v>45002</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E30" s="13" t="s">
+      <c r="E30" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="F30" s="13" t="s">
+      <c r="F30" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="G30" s="13" t="s">
+      <c r="G30" s="11" t="s">
         <v>20</v>
       </c>
       <c r="H30" s="3">
@@ -2324,16 +2477,22 @@
       <c r="I30" s="3">
         <v>30.69041095890411</v>
       </c>
-      <c r="J30" s="13">
+      <c r="J30" s="11">
         <v>2</v>
       </c>
       <c r="K30">
         <v>0</v>
+      </c>
+      <c r="L30">
+        <v>8</v>
+      </c>
+      <c r="M30">
+        <v>3</v>
       </c>
       <c r="N30">
         <v>34</v>
       </c>
-      <c r="O30" s="7">
+      <c r="O30" s="6">
         <v>50.966999999999999</v>
       </c>
     </row>
@@ -2344,19 +2503,19 @@
       <c r="B31" s="1">
         <v>2023</v>
       </c>
-      <c r="C31" s="18">
+      <c r="C31" s="16">
         <v>45002</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E31" s="13" t="s">
+      <c r="E31" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="F31" s="13" t="s">
+      <c r="F31" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="G31" s="13" t="s">
+      <c r="G31" s="11" t="s">
         <v>26</v>
       </c>
       <c r="H31" s="3">
@@ -2365,16 +2524,22 @@
       <c r="I31" s="3">
         <v>22.205479452054796</v>
       </c>
-      <c r="J31" s="13">
+      <c r="J31" s="11">
         <v>3</v>
       </c>
       <c r="K31">
         <v>0</v>
+      </c>
+      <c r="L31">
+        <v>8</v>
+      </c>
+      <c r="M31">
+        <v>3</v>
       </c>
       <c r="N31">
         <v>24</v>
       </c>
-      <c r="O31" s="7">
+      <c r="O31" s="6">
         <v>50.966999999999999</v>
       </c>
     </row>
@@ -2391,13 +2556,13 @@
       <c r="D32" t="s">
         <v>14</v>
       </c>
-      <c r="E32" s="21" t="s">
+      <c r="E32" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="F32" s="21" t="s">
+      <c r="F32" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="G32" s="21" t="s">
+      <c r="G32" s="19" t="s">
         <v>20</v>
       </c>
       <c r="H32" s="3">
@@ -2406,11 +2571,17 @@
       <c r="I32" s="3">
         <v>30.641095890410959</v>
       </c>
-      <c r="J32" s="24">
+      <c r="J32" s="22">
         <v>1</v>
       </c>
       <c r="K32">
         <v>20</v>
+      </c>
+      <c r="L32">
+        <v>8</v>
+      </c>
+      <c r="M32">
+        <v>2</v>
       </c>
       <c r="N32">
         <v>42</v>
@@ -2432,13 +2603,13 @@
       <c r="D33" t="s">
         <v>14</v>
       </c>
-      <c r="E33" s="21" t="s">
+      <c r="E33" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="F33" s="21" t="s">
+      <c r="F33" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="G33" s="21" t="s">
+      <c r="G33" s="19" t="s">
         <v>30</v>
       </c>
       <c r="H33" s="3">
@@ -2447,11 +2618,17 @@
       <c r="I33" s="3">
         <v>25.271232876712329</v>
       </c>
-      <c r="J33" s="24">
+      <c r="J33" s="22">
         <v>2</v>
       </c>
       <c r="K33">
         <v>0</v>
+      </c>
+      <c r="L33">
+        <v>10</v>
+      </c>
+      <c r="M33">
+        <v>3</v>
       </c>
       <c r="N33">
         <v>32</v>
@@ -2473,13 +2650,13 @@
       <c r="D34" t="s">
         <v>14</v>
       </c>
-      <c r="E34" s="21" t="s">
+      <c r="E34" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="F34" s="21" t="s">
+      <c r="F34" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="G34" s="21" t="s">
+      <c r="G34" s="19" t="s">
         <v>23</v>
       </c>
       <c r="H34" s="3">
@@ -2488,11 +2665,17 @@
       <c r="I34" s="3">
         <v>22.997260273972604</v>
       </c>
-      <c r="J34" s="24">
+      <c r="J34" s="22">
         <v>3</v>
       </c>
       <c r="K34">
         <v>0</v>
+      </c>
+      <c r="L34">
+        <v>6</v>
+      </c>
+      <c r="M34">
+        <v>3</v>
       </c>
       <c r="N34">
         <v>26</v>
@@ -2514,13 +2697,13 @@
       <c r="D35" t="s">
         <v>18</v>
       </c>
-      <c r="E35" s="13" t="s">
+      <c r="E35" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="F35" s="13" t="s">
+      <c r="F35" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="G35" s="13" t="s">
+      <c r="G35" s="11" t="s">
         <v>16</v>
       </c>
       <c r="H35" s="3">
@@ -2529,16 +2712,22 @@
       <c r="I35" s="3">
         <v>26.947945205479453</v>
       </c>
-      <c r="J35" s="24">
+      <c r="J35" s="22">
         <v>1</v>
       </c>
       <c r="K35">
         <v>20</v>
       </c>
+      <c r="L35">
+        <v>3</v>
+      </c>
+      <c r="M35">
+        <v>2</v>
+      </c>
       <c r="N35">
         <v>32</v>
       </c>
-      <c r="O35" s="7">
+      <c r="O35" s="6">
         <v>53.28</v>
       </c>
     </row>
@@ -2555,13 +2744,13 @@
       <c r="D36" t="s">
         <v>18</v>
       </c>
-      <c r="E36" s="13" t="s">
+      <c r="E36" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="F36" s="13" t="s">
+      <c r="F36" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="G36" s="13" t="s">
+      <c r="G36" s="11" t="s">
         <v>30</v>
       </c>
       <c r="H36" s="3">
@@ -2570,16 +2759,22 @@
       <c r="I36" s="3">
         <v>23.493150684931507</v>
       </c>
-      <c r="J36" s="24">
+      <c r="J36" s="22">
         <v>2</v>
       </c>
       <c r="K36">
         <v>0</v>
+      </c>
+      <c r="L36">
+        <v>9</v>
+      </c>
+      <c r="M36">
+        <v>2</v>
       </c>
       <c r="N36">
         <v>31</v>
       </c>
-      <c r="O36" s="7">
+      <c r="O36" s="6">
         <v>53.28</v>
       </c>
     </row>
@@ -2596,13 +2791,13 @@
       <c r="D37" t="s">
         <v>18</v>
       </c>
-      <c r="E37" s="13" t="s">
+      <c r="E37" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="F37" s="13" t="s">
+      <c r="F37" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="G37" s="13" t="s">
+      <c r="G37" s="11" t="s">
         <v>20</v>
       </c>
       <c r="H37" s="3">
@@ -2611,16 +2806,22 @@
       <c r="I37" s="3">
         <v>30.276712328767122</v>
       </c>
-      <c r="J37" s="24">
+      <c r="J37" s="22">
         <v>3</v>
       </c>
       <c r="K37">
         <v>0</v>
+      </c>
+      <c r="L37">
+        <v>7</v>
+      </c>
+      <c r="M37">
+        <v>2</v>
       </c>
       <c r="N37">
         <v>23</v>
       </c>
-      <c r="O37" s="7">
+      <c r="O37" s="6">
         <v>53.28</v>
       </c>
     </row>
@@ -2637,13 +2838,13 @@
       <c r="D38" t="s">
         <v>14</v>
       </c>
-      <c r="E38" s="21" t="s">
+      <c r="E38" s="19" t="s">
         <v>85</v>
       </c>
-      <c r="F38" s="21" t="s">
+      <c r="F38" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="G38" s="22" t="s">
+      <c r="G38" s="20" t="s">
         <v>69</v>
       </c>
       <c r="H38" s="3">
@@ -2652,11 +2853,17 @@
       <c r="I38" s="3">
         <v>27.561643835616437</v>
       </c>
-      <c r="J38" s="24">
+      <c r="J38" s="22">
         <v>1</v>
       </c>
       <c r="K38">
         <v>0</v>
+      </c>
+      <c r="L38">
+        <v>11</v>
+      </c>
+      <c r="M38">
+        <v>7</v>
       </c>
       <c r="N38">
         <v>48</v>
@@ -2678,13 +2885,13 @@
       <c r="D39" t="s">
         <v>14</v>
       </c>
-      <c r="E39" s="21" t="s">
+      <c r="E39" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="F39" s="21" t="s">
+      <c r="F39" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="G39" s="22" t="s">
+      <c r="G39" s="20" t="s">
         <v>23</v>
       </c>
       <c r="H39" s="3">
@@ -2693,11 +2900,17 @@
       <c r="I39" s="3">
         <v>22.983561643835618</v>
       </c>
-      <c r="J39" s="24">
+      <c r="J39" s="22">
         <v>2</v>
       </c>
       <c r="K39">
         <v>0</v>
+      </c>
+      <c r="L39">
+        <v>10</v>
+      </c>
+      <c r="M39">
+        <v>2</v>
       </c>
       <c r="N39">
         <v>35</v>
@@ -2719,13 +2932,13 @@
       <c r="D40" t="s">
         <v>14</v>
       </c>
-      <c r="E40" s="21" t="s">
+      <c r="E40" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="F40" s="21" t="s">
+      <c r="F40" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="G40" s="22" t="s">
+      <c r="G40" s="20" t="s">
         <v>26</v>
       </c>
       <c r="H40" s="3">
@@ -2734,11 +2947,17 @@
       <c r="I40" s="3">
         <v>19.86849315068493</v>
       </c>
-      <c r="J40" s="24">
-        <v>3</v>
-      </c>
-      <c r="K40" s="4">
-        <v>0</v>
+      <c r="J40" s="22">
+        <v>3</v>
+      </c>
+      <c r="K40">
+        <v>0</v>
+      </c>
+      <c r="L40">
+        <v>10</v>
+      </c>
+      <c r="M40">
+        <v>1</v>
       </c>
       <c r="N40">
         <v>29</v>
@@ -2760,13 +2979,13 @@
       <c r="D41" t="s">
         <v>14</v>
       </c>
-      <c r="E41" s="13" t="s">
+      <c r="E41" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F41" s="6" t="s">
+      <c r="F41" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="G41" s="23" t="s">
+      <c r="G41" s="21" t="s">
         <v>23</v>
       </c>
       <c r="H41" s="3">
@@ -2775,11 +2994,17 @@
       <c r="I41" s="3">
         <v>22.906849315068492</v>
       </c>
-      <c r="J41" s="24">
+      <c r="J41" s="22">
         <v>1</v>
       </c>
       <c r="K41">
         <v>20</v>
+      </c>
+      <c r="L41">
+        <v>9</v>
+      </c>
+      <c r="M41">
+        <v>5</v>
       </c>
       <c r="N41">
         <v>54</v>
@@ -2801,13 +3026,13 @@
       <c r="D42" t="s">
         <v>14</v>
       </c>
-      <c r="E42" s="13" t="s">
+      <c r="E42" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="F42" s="13" t="s">
+      <c r="F42" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="G42" s="23" t="s">
+      <c r="G42" s="21" t="s">
         <v>42</v>
       </c>
       <c r="H42" s="3">
@@ -2816,11 +3041,17 @@
       <c r="I42" s="3">
         <v>23.509589041095889</v>
       </c>
-      <c r="J42" s="24">
+      <c r="J42" s="22">
         <v>2</v>
       </c>
       <c r="K42">
         <v>20</v>
+      </c>
+      <c r="L42">
+        <v>6</v>
+      </c>
+      <c r="M42">
+        <v>3</v>
       </c>
       <c r="N42">
         <v>45</v>
@@ -2842,13 +3073,13 @@
       <c r="D43" t="s">
         <v>14</v>
       </c>
-      <c r="E43" s="13" t="s">
+      <c r="E43" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="F43" s="13" t="s">
+      <c r="F43" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="G43" s="23" t="s">
+      <c r="G43" s="21" t="s">
         <v>93</v>
       </c>
       <c r="H43" s="3">
@@ -2857,11 +3088,17 @@
       <c r="I43" s="3">
         <v>28.052054794520547</v>
       </c>
-      <c r="J43" s="24">
+      <c r="J43" s="22">
         <v>3</v>
       </c>
       <c r="K43">
         <v>20</v>
+      </c>
+      <c r="L43">
+        <v>5</v>
+      </c>
+      <c r="M43">
+        <v>0</v>
       </c>
       <c r="N43">
         <v>29</v>
@@ -2883,13 +3120,13 @@
       <c r="D44" t="s">
         <v>14</v>
       </c>
-      <c r="E44" s="21" t="s">
+      <c r="E44" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="F44" s="21" t="s">
+      <c r="F44" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="G44" s="22" t="s">
+      <c r="G44" s="20" t="s">
         <v>30</v>
       </c>
       <c r="H44" s="3">
@@ -2898,11 +3135,17 @@
       <c r="I44" s="3">
         <v>23.016438356164382</v>
       </c>
-      <c r="J44" s="24">
+      <c r="J44" s="22">
         <v>1</v>
       </c>
       <c r="K44">
         <v>0</v>
+      </c>
+      <c r="L44">
+        <v>8</v>
+      </c>
+      <c r="M44">
+        <v>5</v>
       </c>
       <c r="N44">
         <v>33</v>
@@ -2924,13 +3167,13 @@
       <c r="D45" t="s">
         <v>14</v>
       </c>
-      <c r="E45" s="21" t="s">
+      <c r="E45" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="F45" s="21" t="s">
+      <c r="F45" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="G45" s="22" t="s">
+      <c r="G45" s="20" t="s">
         <v>23</v>
       </c>
       <c r="H45" s="3">
@@ -2939,11 +3182,17 @@
       <c r="I45" s="3">
         <v>21.339726027397262</v>
       </c>
-      <c r="J45" s="24">
+      <c r="J45" s="22">
         <v>2</v>
       </c>
       <c r="K45">
         <v>0</v>
+      </c>
+      <c r="L45">
+        <v>7</v>
+      </c>
+      <c r="M45">
+        <v>1</v>
       </c>
       <c r="N45">
         <v>23</v>
@@ -2965,13 +3214,13 @@
       <c r="D46" t="s">
         <v>14</v>
       </c>
-      <c r="E46" s="21" t="s">
+      <c r="E46" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="F46" s="21" t="s">
+      <c r="F46" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="G46" s="22" t="s">
+      <c r="G46" s="20" t="s">
         <v>20</v>
       </c>
       <c r="H46" s="3">
@@ -2980,11 +3229,17 @@
       <c r="I46" s="3">
         <v>29.8</v>
       </c>
-      <c r="J46" s="24">
+      <c r="J46" s="22">
         <v>3</v>
       </c>
       <c r="K46">
         <v>0</v>
+      </c>
+      <c r="L46">
+        <v>6</v>
+      </c>
+      <c r="M46">
+        <v>1</v>
       </c>
       <c r="N46">
         <v>18</v>
@@ -3006,13 +3261,13 @@
       <c r="D47" t="s">
         <v>18</v>
       </c>
-      <c r="E47" s="6" t="s">
+      <c r="E47" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="F47" s="6" t="s">
+      <c r="F47" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="G47" s="6" t="s">
+      <c r="G47" s="5" t="s">
         <v>15</v>
       </c>
       <c r="H47" s="3">
@@ -3021,11 +3276,17 @@
       <c r="I47" s="3">
         <v>39.049315068493151</v>
       </c>
-      <c r="J47" s="7">
+      <c r="J47" s="6">
         <v>1</v>
       </c>
       <c r="K47">
         <v>0</v>
+      </c>
+      <c r="L47">
+        <v>9</v>
+      </c>
+      <c r="M47">
+        <v>4</v>
       </c>
       <c r="N47">
         <v>35</v>
@@ -3047,13 +3308,13 @@
       <c r="D48" t="s">
         <v>18</v>
       </c>
-      <c r="E48" s="6" t="s">
+      <c r="E48" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="F48" s="6" t="s">
+      <c r="F48" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="G48" s="6" t="s">
+      <c r="G48" s="5" t="s">
         <v>30</v>
       </c>
       <c r="H48" s="3">
@@ -3062,11 +3323,17 @@
       <c r="I48" s="3">
         <v>21.758904109589039</v>
       </c>
-      <c r="J48" s="7">
+      <c r="J48" s="6">
         <v>2</v>
       </c>
       <c r="K48">
         <v>0</v>
+      </c>
+      <c r="L48">
+        <v>9</v>
+      </c>
+      <c r="M48">
+        <v>2</v>
       </c>
       <c r="N48">
         <v>30</v>
@@ -3076,25 +3343,25 @@
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A49" s="8" t="s">
+      <c r="A49" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B49" s="8">
+      <c r="B49" s="7">
         <v>2021</v>
       </c>
-      <c r="C49" s="9">
+      <c r="C49" s="8">
         <v>44493</v>
       </c>
-      <c r="D49" s="8" t="s">
+      <c r="D49" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E49" s="6" t="s">
+      <c r="E49" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F49" s="6" t="s">
+      <c r="F49" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="G49" s="6" t="s">
+      <c r="G49" s="5" t="s">
         <v>28</v>
       </c>
       <c r="H49" s="3">
@@ -3103,11 +3370,17 @@
       <c r="I49" s="3">
         <v>31.24931506849315</v>
       </c>
-      <c r="J49" s="7">
+      <c r="J49" s="6">
         <v>3</v>
       </c>
       <c r="K49">
         <v>0</v>
+      </c>
+      <c r="L49">
+        <v>10</v>
+      </c>
+      <c r="M49">
+        <v>1</v>
       </c>
       <c r="N49">
         <v>24</v>
@@ -3117,16 +3390,16 @@
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A50" s="8" t="s">
+      <c r="A50" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B50" s="8">
+      <c r="B50" s="7">
         <v>2021</v>
       </c>
-      <c r="C50" s="9">
+      <c r="C50" s="8">
         <v>44450</v>
       </c>
-      <c r="D50" s="8" t="s">
+      <c r="D50" s="7" t="s">
         <v>14</v>
       </c>
       <c r="E50" s="1" t="s">
@@ -3144,11 +3417,17 @@
       <c r="I50" s="3">
         <v>23.252054794520546</v>
       </c>
-      <c r="J50" s="7">
+      <c r="J50" s="6">
         <v>1</v>
       </c>
       <c r="K50">
         <v>0</v>
+      </c>
+      <c r="L50">
+        <v>11</v>
+      </c>
+      <c r="M50">
+        <v>10</v>
       </c>
       <c r="N50">
         <v>53</v>
@@ -3158,16 +3437,16 @@
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A51" s="8" t="s">
+      <c r="A51" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B51" s="8">
+      <c r="B51" s="7">
         <v>2021</v>
       </c>
-      <c r="C51" s="9">
+      <c r="C51" s="8">
         <v>44450</v>
       </c>
-      <c r="D51" s="8" t="s">
+      <c r="D51" s="7" t="s">
         <v>14</v>
       </c>
       <c r="E51" s="1" t="s">
@@ -3185,10 +3464,16 @@
       <c r="I51" s="3">
         <v>27.358904109589041</v>
       </c>
-      <c r="J51" s="7">
+      <c r="J51" s="6">
         <v>2</v>
       </c>
       <c r="K51">
+        <v>0</v>
+      </c>
+      <c r="L51">
+        <v>9</v>
+      </c>
+      <c r="M51">
         <v>0</v>
       </c>
       <c r="N51">
@@ -3199,16 +3484,16 @@
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A52" s="10" t="s">
+      <c r="A52" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="B52" s="10">
+      <c r="B52" s="9">
         <v>2021</v>
       </c>
-      <c r="C52" s="11">
+      <c r="C52" s="10">
         <v>44450</v>
       </c>
-      <c r="D52" s="10" t="s">
+      <c r="D52" s="9" t="s">
         <v>14</v>
       </c>
       <c r="E52" s="1" t="s">
@@ -3226,10 +3511,16 @@
       <c r="I52" s="3">
         <v>20.873972602739727</v>
       </c>
-      <c r="J52" s="7">
-        <v>3</v>
-      </c>
-      <c r="K52" s="12">
+      <c r="J52" s="6">
+        <v>3</v>
+      </c>
+      <c r="K52">
+        <v>0</v>
+      </c>
+      <c r="L52">
+        <v>10</v>
+      </c>
+      <c r="M52">
         <v>0</v>
       </c>
       <c r="N52">
@@ -3240,16 +3531,16 @@
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A53" s="13" t="s">
+      <c r="A53" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="B53" s="13">
+      <c r="B53" s="11">
         <v>2021</v>
       </c>
-      <c r="C53" s="14">
+      <c r="C53" s="12">
         <v>44415</v>
       </c>
-      <c r="D53" s="13" t="s">
+      <c r="D53" s="11" t="s">
         <v>22</v>
       </c>
       <c r="E53" t="s">
@@ -3267,30 +3558,36 @@
       <c r="I53" s="3">
         <v>29.304109589041097</v>
       </c>
-      <c r="J53" s="6">
+      <c r="J53" s="5">
         <v>1</v>
       </c>
-      <c r="K53" s="13">
+      <c r="K53" s="11">
         <v>20</v>
       </c>
-      <c r="N53" s="13">
+      <c r="L53">
+        <v>12</v>
+      </c>
+      <c r="M53">
+        <v>10</v>
+      </c>
+      <c r="N53" s="11">
         <v>78</v>
       </c>
-      <c r="O53" s="7">
+      <c r="O53" s="6">
         <v>54.947000000000003</v>
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A54" s="13" t="s">
+      <c r="A54" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="B54" s="13">
+      <c r="B54" s="11">
         <v>2021</v>
       </c>
-      <c r="C54" s="14">
+      <c r="C54" s="12">
         <v>44415</v>
       </c>
-      <c r="D54" s="13" t="s">
+      <c r="D54" s="11" t="s">
         <v>22</v>
       </c>
       <c r="E54" t="s">
@@ -3308,30 +3605,36 @@
       <c r="I54" s="3">
         <v>29.084931506849315</v>
       </c>
-      <c r="J54" s="6">
+      <c r="J54" s="5">
         <v>2</v>
       </c>
-      <c r="K54" s="13">
+      <c r="K54" s="11">
         <v>20</v>
       </c>
-      <c r="N54" s="13">
+      <c r="L54">
+        <v>7</v>
+      </c>
+      <c r="M54">
+        <v>0</v>
+      </c>
+      <c r="N54" s="11">
         <v>35</v>
       </c>
-      <c r="O54" s="7">
+      <c r="O54" s="6">
         <v>54.947000000000003</v>
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A55" s="13" t="s">
+      <c r="A55" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="B55" s="13">
+      <c r="B55" s="11">
         <v>2021</v>
       </c>
-      <c r="C55" s="14">
+      <c r="C55" s="12">
         <v>44415</v>
       </c>
-      <c r="D55" s="13" t="s">
+      <c r="D55" s="11" t="s">
         <v>22</v>
       </c>
       <c r="E55" t="s">
@@ -3349,39 +3652,45 @@
       <c r="I55" s="3">
         <v>22.041095890410958</v>
       </c>
-      <c r="J55" s="6">
-        <v>3</v>
-      </c>
-      <c r="K55" s="13">
+      <c r="J55" s="5">
+        <v>3</v>
+      </c>
+      <c r="K55" s="11">
         <v>20</v>
       </c>
-      <c r="N55" s="13">
+      <c r="L55">
+        <v>3</v>
+      </c>
+      <c r="M55">
+        <v>0</v>
+      </c>
+      <c r="N55" s="11">
         <v>26</v>
       </c>
-      <c r="O55" s="7">
+      <c r="O55" s="6">
         <v>54.947000000000003</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A56" s="15" t="s">
+      <c r="A56" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B56" s="15">
+      <c r="B56" s="13">
         <v>2021</v>
       </c>
       <c r="C56" s="2">
         <v>44387</v>
       </c>
-      <c r="D56" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E56" s="6" t="s">
+      <c r="D56" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E56" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="F56" s="6" t="s">
+      <c r="F56" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="G56" s="6" t="s">
+      <c r="G56" s="5" t="s">
         <v>39</v>
       </c>
       <c r="H56" s="3">
@@ -3390,11 +3699,17 @@
       <c r="I56" s="3">
         <v>24.772602739726029</v>
       </c>
-      <c r="J56" s="7">
+      <c r="J56" s="6">
         <v>1</v>
       </c>
       <c r="K56">
         <v>0</v>
+      </c>
+      <c r="L56">
+        <v>12</v>
+      </c>
+      <c r="M56">
+        <v>7</v>
       </c>
       <c r="N56">
         <v>50</v>
@@ -3404,25 +3719,25 @@
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A57" s="15" t="s">
+      <c r="A57" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B57" s="15">
+      <c r="B57" s="13">
         <v>2021</v>
       </c>
       <c r="C57" s="2">
         <v>44387</v>
       </c>
-      <c r="D57" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E57" s="6" t="s">
+      <c r="D57" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E57" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="F57" s="6" t="s">
+      <c r="F57" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="G57" s="6" t="s">
+      <c r="G57" s="5" t="s">
         <v>38</v>
       </c>
       <c r="H57" s="3">
@@ -3431,11 +3746,17 @@
       <c r="I57" s="3">
         <v>17.663013698630138</v>
       </c>
-      <c r="J57" s="7">
+      <c r="J57" s="6">
         <v>2</v>
       </c>
       <c r="K57">
         <v>0</v>
+      </c>
+      <c r="L57">
+        <v>11</v>
+      </c>
+      <c r="M57">
+        <v>4</v>
       </c>
       <c r="N57">
         <v>41</v>
@@ -3445,25 +3766,25 @@
       </c>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A58" s="15" t="s">
+      <c r="A58" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B58" s="15">
+      <c r="B58" s="13">
         <v>2021</v>
       </c>
       <c r="C58" s="2">
         <v>44387</v>
       </c>
-      <c r="D58" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E58" s="6" t="s">
+      <c r="D58" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E58" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="F58" s="6" t="s">
+      <c r="F58" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="G58" s="6" t="s">
+      <c r="G58" s="5" t="s">
         <v>114</v>
       </c>
       <c r="H58" s="3">
@@ -3472,11 +3793,17 @@
       <c r="I58" s="3">
         <v>24.142465753424659</v>
       </c>
-      <c r="J58" s="7">
-        <v>3</v>
-      </c>
-      <c r="K58" s="4">
-        <v>0</v>
+      <c r="J58" s="6">
+        <v>3</v>
+      </c>
+      <c r="K58">
+        <v>0</v>
+      </c>
+      <c r="L58">
+        <v>12</v>
+      </c>
+      <c r="M58">
+        <v>1</v>
       </c>
       <c r="N58">
         <v>32</v>
@@ -3486,16 +3813,16 @@
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A59" s="8" t="s">
+      <c r="A59" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B59" s="8">
+      <c r="B59" s="7">
         <v>2020</v>
       </c>
-      <c r="C59" s="9">
+      <c r="C59" s="8">
         <v>43891</v>
       </c>
-      <c r="D59" s="8" t="s">
+      <c r="D59" s="7" t="s">
         <v>18</v>
       </c>
       <c r="E59" s="1" t="s">
@@ -3513,30 +3840,36 @@
       <c r="I59" s="3">
         <v>28.767123287671232</v>
       </c>
-      <c r="J59" s="7">
+      <c r="J59" s="6">
         <v>1</v>
       </c>
       <c r="K59">
         <v>0</v>
+      </c>
+      <c r="L59">
+        <v>11</v>
+      </c>
+      <c r="M59">
+        <v>3</v>
       </c>
       <c r="N59">
         <v>36</v>
       </c>
-      <c r="O59" s="6">
+      <c r="O59" s="5">
         <v>50.908000000000001</v>
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A60" s="8" t="s">
+      <c r="A60" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B60" s="8">
+      <c r="B60" s="7">
         <v>2020</v>
       </c>
-      <c r="C60" s="9">
+      <c r="C60" s="8">
         <v>43891</v>
       </c>
-      <c r="D60" s="8" t="s">
+      <c r="D60" s="7" t="s">
         <v>18</v>
       </c>
       <c r="E60" s="1" t="s">
@@ -3554,30 +3887,36 @@
       <c r="I60" s="3">
         <v>20.109589041095891</v>
       </c>
-      <c r="J60" s="7">
+      <c r="J60" s="6">
         <v>2</v>
       </c>
-      <c r="K60" s="4">
-        <v>0</v>
+      <c r="K60">
+        <v>0</v>
+      </c>
+      <c r="L60">
+        <v>6</v>
+      </c>
+      <c r="M60">
+        <v>3</v>
       </c>
       <c r="N60">
         <v>24</v>
       </c>
-      <c r="O60" s="6">
+      <c r="O60" s="5">
         <v>50.908000000000001</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A61" s="8" t="s">
+      <c r="A61" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B61" s="8">
+      <c r="B61" s="7">
         <v>2020</v>
       </c>
-      <c r="C61" s="9">
+      <c r="C61" s="8">
         <v>43891</v>
       </c>
-      <c r="D61" s="8" t="s">
+      <c r="D61" s="7" t="s">
         <v>18</v>
       </c>
       <c r="E61" s="1" t="s">
@@ -3595,39 +3934,45 @@
       <c r="I61" s="3">
         <v>22.019178082191782</v>
       </c>
-      <c r="J61" s="7">
-        <v>3</v>
-      </c>
-      <c r="K61" s="4">
-        <v>0</v>
+      <c r="J61" s="6">
+        <v>3</v>
+      </c>
+      <c r="K61">
+        <v>0</v>
+      </c>
+      <c r="L61">
+        <v>6</v>
+      </c>
+      <c r="M61">
+        <v>2</v>
       </c>
       <c r="N61">
         <v>20</v>
       </c>
-      <c r="O61" s="6">
+      <c r="O61" s="5">
         <v>50.908000000000001</v>
       </c>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A62" s="15" t="s">
+      <c r="A62" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="B62" s="15">
+      <c r="B62" s="13">
         <v>2020</v>
       </c>
       <c r="C62" s="2">
         <v>43856</v>
       </c>
-      <c r="D62" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="E62" s="6" t="s">
+      <c r="D62" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="E62" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="F62" s="6" t="s">
+      <c r="F62" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="G62" s="6" t="s">
+      <c r="G62" s="5" t="s">
         <v>28</v>
       </c>
       <c r="H62" s="3">
@@ -3636,37 +3981,43 @@
       <c r="I62" s="3">
         <v>27.772602739726029</v>
       </c>
-      <c r="J62" s="7">
+      <c r="J62" s="6">
         <v>1</v>
       </c>
       <c r="K62">
         <v>0</v>
+      </c>
+      <c r="L62">
+        <v>8</v>
+      </c>
+      <c r="M62">
+        <v>4</v>
       </c>
       <c r="N62">
         <v>30</v>
       </c>
-      <c r="O62" s="26"/>
+      <c r="O62" s="24"/>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A63" s="15" t="s">
+      <c r="A63" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="B63" s="15">
+      <c r="B63" s="13">
         <v>2020</v>
       </c>
       <c r="C63" s="2">
         <v>43856</v>
       </c>
-      <c r="D63" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="E63" s="6" t="s">
+      <c r="D63" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="E63" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="F63" s="6" t="s">
+      <c r="F63" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="G63" s="6" t="s">
+      <c r="G63" s="5" t="s">
         <v>16</v>
       </c>
       <c r="H63" s="3">
@@ -3675,37 +4026,43 @@
       <c r="I63" s="3">
         <v>24.224657534246575</v>
       </c>
-      <c r="J63" s="7">
+      <c r="J63" s="6">
         <v>2</v>
       </c>
       <c r="K63">
         <v>0</v>
+      </c>
+      <c r="L63">
+        <v>9</v>
+      </c>
+      <c r="M63">
+        <v>2</v>
       </c>
       <c r="N63">
         <v>28</v>
       </c>
-      <c r="O63" s="26"/>
+      <c r="O63" s="24"/>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A64" s="15" t="s">
+      <c r="A64" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="B64" s="15">
+      <c r="B64" s="13">
         <v>2020</v>
       </c>
       <c r="C64" s="2">
         <v>43856</v>
       </c>
-      <c r="D64" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="E64" s="6" t="s">
+      <c r="D64" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="E64" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="F64" s="6" t="s">
+      <c r="F64" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="G64" s="6" t="s">
+      <c r="G64" s="5" t="s">
         <v>69</v>
       </c>
       <c r="H64" s="3">
@@ -3714,28 +4071,34 @@
       <c r="I64" s="3">
         <v>25.104109589041094</v>
       </c>
-      <c r="J64" s="7">
-        <v>3</v>
-      </c>
-      <c r="K64" s="4">
-        <v>0</v>
+      <c r="J64" s="6">
+        <v>3</v>
+      </c>
+      <c r="K64">
+        <v>0</v>
+      </c>
+      <c r="L64">
+        <v>9</v>
+      </c>
+      <c r="M64">
+        <v>2</v>
       </c>
       <c r="N64">
         <v>24</v>
       </c>
-      <c r="O64" s="26"/>
+      <c r="O64" s="24"/>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A65" s="15" t="s">
+      <c r="A65" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="B65" s="15">
+      <c r="B65" s="13">
         <v>2019</v>
       </c>
       <c r="C65" s="2">
         <v>43814</v>
       </c>
-      <c r="D65" s="15" t="s">
+      <c r="D65" s="13" t="s">
         <v>14</v>
       </c>
       <c r="E65" s="1" t="s">
@@ -3753,30 +4116,36 @@
       <c r="I65" s="3">
         <v>28.024657534246575</v>
       </c>
-      <c r="J65" s="7">
+      <c r="J65" s="6">
         <v>1</v>
       </c>
       <c r="K65">
         <v>20</v>
       </c>
+      <c r="L65">
+        <v>11</v>
+      </c>
+      <c r="M65">
+        <v>5</v>
+      </c>
       <c r="N65">
         <v>56</v>
       </c>
-      <c r="O65" s="26">
+      <c r="O65" s="24">
         <v>48.262</v>
       </c>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A66" s="15" t="s">
+      <c r="A66" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="B66" s="15">
+      <c r="B66" s="13">
         <v>2019</v>
       </c>
       <c r="C66" s="2">
         <v>43814</v>
       </c>
-      <c r="D66" s="15" t="s">
+      <c r="D66" s="13" t="s">
         <v>14</v>
       </c>
       <c r="E66" s="1" t="s">
@@ -3794,30 +4163,36 @@
       <c r="I66" s="3">
         <v>19.898630136986302</v>
       </c>
-      <c r="J66" s="7">
+      <c r="J66" s="6">
         <v>2</v>
       </c>
       <c r="K66">
         <v>20</v>
       </c>
+      <c r="L66">
+        <v>8</v>
+      </c>
+      <c r="M66">
+        <v>2</v>
+      </c>
       <c r="N66">
         <v>51</v>
       </c>
-      <c r="O66" s="26">
+      <c r="O66" s="24">
         <v>48.262</v>
       </c>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A67" s="15" t="s">
+      <c r="A67" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="B67" s="15">
+      <c r="B67" s="13">
         <v>2019</v>
       </c>
       <c r="C67" s="2">
         <v>43814</v>
       </c>
-      <c r="D67" s="15" t="s">
+      <c r="D67" s="13" t="s">
         <v>14</v>
       </c>
       <c r="E67" s="1" t="s">
@@ -3835,39 +4210,45 @@
       <c r="I67" s="3">
         <v>33.095890410958901</v>
       </c>
-      <c r="J67" s="7">
+      <c r="J67" s="6">
         <v>3</v>
       </c>
       <c r="K67">
         <v>20</v>
       </c>
+      <c r="L67">
+        <v>4</v>
+      </c>
+      <c r="M67">
+        <v>1</v>
+      </c>
       <c r="N67">
         <v>32</v>
       </c>
-      <c r="O67" s="26">
+      <c r="O67" s="24">
         <v>48.262</v>
       </c>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A68" s="15" t="s">
+      <c r="A68" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="B68" s="15">
+      <c r="B68" s="13">
         <v>2019</v>
       </c>
       <c r="C68" s="2">
         <v>43807</v>
       </c>
-      <c r="D68" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="E68" s="6" t="s">
+      <c r="D68" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="E68" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="F68" s="6" t="s">
+      <c r="F68" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="G68" s="6" t="s">
+      <c r="G68" s="5" t="s">
         <v>42</v>
       </c>
       <c r="H68" s="3">
@@ -3876,39 +4257,45 @@
       <c r="I68" s="3">
         <v>23.789041095890411</v>
       </c>
-      <c r="J68" s="7">
+      <c r="J68" s="6">
         <v>1</v>
       </c>
       <c r="K68">
         <v>0</v>
+      </c>
+      <c r="L68">
+        <v>10</v>
+      </c>
+      <c r="M68">
+        <v>6</v>
       </c>
       <c r="N68">
         <v>42</v>
       </c>
-      <c r="O68" s="26">
+      <c r="O68" s="24">
         <v>49.936</v>
       </c>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A69" s="15" t="s">
+      <c r="A69" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="B69" s="15">
+      <c r="B69" s="13">
         <v>2019</v>
       </c>
       <c r="C69" s="2">
         <v>43807</v>
       </c>
-      <c r="D69" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="E69" s="6" t="s">
+      <c r="D69" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="E69" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="F69" s="6" t="s">
+      <c r="F69" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="G69" s="6" t="s">
+      <c r="G69" s="5" t="s">
         <v>99</v>
       </c>
       <c r="H69" s="3">
@@ -3917,39 +4304,45 @@
       <c r="I69" s="3">
         <v>23.55890410958904</v>
       </c>
-      <c r="J69" s="7">
+      <c r="J69" s="6">
         <v>2</v>
       </c>
       <c r="K69">
         <v>0</v>
+      </c>
+      <c r="L69">
+        <v>11</v>
+      </c>
+      <c r="M69">
+        <v>1</v>
       </c>
       <c r="N69">
         <v>32</v>
       </c>
-      <c r="O69" s="26">
+      <c r="O69" s="24">
         <v>49.936</v>
       </c>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A70" s="15" t="s">
+      <c r="A70" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="B70" s="15">
+      <c r="B70" s="13">
         <v>2019</v>
       </c>
       <c r="C70" s="2">
         <v>43807</v>
       </c>
-      <c r="D70" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="E70" s="6" t="s">
+      <c r="D70" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="E70" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="F70" s="6" t="s">
+      <c r="F70" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="G70" s="6" t="s">
+      <c r="G70" s="5" t="s">
         <v>122</v>
       </c>
       <c r="H70" s="3">
@@ -3958,16 +4351,22 @@
       <c r="I70" s="3">
         <v>23.147945205479452</v>
       </c>
-      <c r="J70" s="7">
+      <c r="J70" s="6">
         <v>3</v>
       </c>
       <c r="K70">
         <v>0</v>
+      </c>
+      <c r="L70">
+        <v>6</v>
+      </c>
+      <c r="M70">
+        <v>1</v>
       </c>
       <c r="N70">
         <v>19</v>
       </c>
-      <c r="O70" s="26">
+      <c r="O70" s="24">
         <v>49.936</v>
       </c>
     </row>
@@ -3999,16 +4398,22 @@
       <c r="I71" s="3">
         <v>31.512328767123286</v>
       </c>
-      <c r="J71" s="7">
+      <c r="J71" s="6">
         <v>1</v>
       </c>
       <c r="K71">
         <v>0</v>
+      </c>
+      <c r="L71">
+        <v>8</v>
+      </c>
+      <c r="M71">
+        <v>3</v>
       </c>
       <c r="N71">
         <v>31</v>
       </c>
-      <c r="O71" s="26">
+      <c r="O71" s="24">
         <v>40.737000000000002</v>
       </c>
     </row>
@@ -4040,16 +4445,22 @@
       <c r="I72" s="3">
         <v>23.12876712328767</v>
       </c>
-      <c r="J72" s="7">
+      <c r="J72" s="6">
         <v>2</v>
       </c>
-      <c r="K72" s="4">
-        <v>0</v>
+      <c r="K72">
+        <v>0</v>
+      </c>
+      <c r="L72">
+        <v>5</v>
+      </c>
+      <c r="M72">
+        <v>3</v>
       </c>
       <c r="N72">
         <v>24</v>
       </c>
-      <c r="O72" s="26">
+      <c r="O72" s="24">
         <v>40.737000000000002</v>
       </c>
     </row>
@@ -4081,39 +4492,45 @@
       <c r="I73" s="3">
         <v>20.449315068493149</v>
       </c>
-      <c r="J73" s="7">
-        <v>3</v>
-      </c>
-      <c r="K73" s="4">
-        <v>0</v>
+      <c r="J73" s="6">
+        <v>3</v>
+      </c>
+      <c r="K73">
+        <v>0</v>
+      </c>
+      <c r="L73">
+        <v>6</v>
+      </c>
+      <c r="M73">
+        <v>2</v>
       </c>
       <c r="N73">
         <v>18</v>
       </c>
-      <c r="O73" s="26">
+      <c r="O73" s="24">
         <v>40.737000000000002</v>
       </c>
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A74" s="8" t="s">
+      <c r="A74" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B74" s="8">
+      <c r="B74" s="7">
         <v>2019</v>
       </c>
-      <c r="C74" s="9">
+      <c r="C74" s="8">
         <v>43777</v>
       </c>
-      <c r="D74" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E74" s="6" t="s">
+      <c r="D74" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E74" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="F74" s="6" t="s">
+      <c r="F74" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="G74" s="6" t="s">
+      <c r="G74" s="5" t="s">
         <v>42</v>
       </c>
       <c r="H74" s="3">
@@ -4122,39 +4539,45 @@
       <c r="I74" s="3">
         <v>25.153424657534245</v>
       </c>
-      <c r="J74" s="7">
+      <c r="J74" s="6">
         <v>1</v>
       </c>
       <c r="K74">
         <v>0</v>
+      </c>
+      <c r="L74">
+        <v>9</v>
+      </c>
+      <c r="M74">
+        <v>6</v>
       </c>
       <c r="N74">
         <v>40</v>
       </c>
-      <c r="O74" s="26">
+      <c r="O74" s="24">
         <v>52.779000000000003</v>
       </c>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A75" s="8" t="s">
+      <c r="A75" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B75" s="8">
+      <c r="B75" s="7">
         <v>2019</v>
       </c>
-      <c r="C75" s="9">
+      <c r="C75" s="8">
         <v>43777</v>
       </c>
-      <c r="D75" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E75" s="6" t="s">
+      <c r="D75" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E75" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F75" s="6" t="s">
+      <c r="F75" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="G75" s="6" t="s">
+      <c r="G75" s="5" t="s">
         <v>28</v>
       </c>
       <c r="H75" s="3">
@@ -4163,39 +4586,45 @@
       <c r="I75" s="3">
         <v>25.19178082191781</v>
       </c>
-      <c r="J75" s="7">
+      <c r="J75" s="6">
         <v>2</v>
       </c>
       <c r="K75">
         <v>0</v>
+      </c>
+      <c r="L75">
+        <v>6</v>
+      </c>
+      <c r="M75">
+        <v>5</v>
       </c>
       <c r="N75">
         <v>31</v>
       </c>
-      <c r="O75" s="26">
+      <c r="O75" s="24">
         <v>52.779000000000003</v>
       </c>
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A76" s="8" t="s">
+      <c r="A76" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B76" s="8">
+      <c r="B76" s="7">
         <v>2019</v>
       </c>
-      <c r="C76" s="9">
+      <c r="C76" s="8">
         <v>43777</v>
       </c>
-      <c r="D76" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E76" s="6" t="s">
+      <c r="D76" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E76" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="F76" s="6" t="s">
+      <c r="F76" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="G76" s="6" t="s">
+      <c r="G76" s="5" t="s">
         <v>15</v>
       </c>
       <c r="H76" s="3">
@@ -4204,30 +4633,36 @@
       <c r="I76" s="3">
         <v>28.463013698630139</v>
       </c>
-      <c r="J76" s="7">
+      <c r="J76" s="6">
         <v>3</v>
       </c>
       <c r="K76">
+        <v>0</v>
+      </c>
+      <c r="L76">
+        <v>8</v>
+      </c>
+      <c r="M76">
         <v>0</v>
       </c>
       <c r="N76">
         <v>19</v>
       </c>
-      <c r="O76" s="26">
+      <c r="O76" s="24">
         <v>52.779000000000003</v>
       </c>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A77" s="15" t="s">
+      <c r="A77" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="B77" s="15">
+      <c r="B77" s="13">
         <v>2019</v>
       </c>
       <c r="C77" s="2">
         <v>43772</v>
       </c>
-      <c r="D77" s="15" t="s">
+      <c r="D77" s="13" t="s">
         <v>14</v>
       </c>
       <c r="E77" s="1" t="s">
@@ -4245,30 +4680,36 @@
       <c r="I77" s="3">
         <v>28.44109589041096</v>
       </c>
-      <c r="J77" s="7">
+      <c r="J77" s="6">
         <v>1</v>
       </c>
       <c r="K77">
         <v>20</v>
       </c>
+      <c r="L77">
+        <v>10</v>
+      </c>
+      <c r="M77">
+        <v>3</v>
+      </c>
       <c r="N77">
         <v>50</v>
       </c>
-      <c r="O77" s="26">
+      <c r="O77" s="24">
         <v>53.268000000000001</v>
       </c>
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A78" s="15" t="s">
+      <c r="A78" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="B78" s="15">
+      <c r="B78" s="13">
         <v>2019</v>
       </c>
       <c r="C78" s="2">
         <v>43772</v>
       </c>
-      <c r="D78" s="15" t="s">
+      <c r="D78" s="13" t="s">
         <v>14</v>
       </c>
       <c r="E78" s="1" t="s">
@@ -4286,30 +4727,36 @@
       <c r="I78" s="3">
         <v>22.991780821917807</v>
       </c>
-      <c r="J78" s="7">
+      <c r="J78" s="6">
         <v>2</v>
       </c>
       <c r="K78">
         <v>20</v>
       </c>
+      <c r="L78">
+        <v>7</v>
+      </c>
+      <c r="M78">
+        <v>3</v>
+      </c>
       <c r="N78">
         <v>44</v>
       </c>
-      <c r="O78" s="26">
+      <c r="O78" s="24">
         <v>53.268000000000001</v>
       </c>
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A79" s="15" t="s">
+      <c r="A79" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="B79" s="15">
+      <c r="B79" s="13">
         <v>2019</v>
       </c>
       <c r="C79" s="2">
         <v>43772</v>
       </c>
-      <c r="D79" s="15" t="s">
+      <c r="D79" s="13" t="s">
         <v>14</v>
       </c>
       <c r="E79" s="1" t="s">
@@ -4327,16 +4774,22 @@
       <c r="I79" s="3">
         <v>19.783561643835615</v>
       </c>
-      <c r="J79" s="7">
+      <c r="J79" s="6">
         <v>3</v>
       </c>
       <c r="K79">
         <v>20</v>
       </c>
+      <c r="L79">
+        <v>5</v>
+      </c>
+      <c r="M79">
+        <v>1</v>
+      </c>
       <c r="N79">
         <v>35</v>
       </c>
-      <c r="O79" s="26">
+      <c r="O79" s="24">
         <v>53.268000000000001</v>
       </c>
     </row>
@@ -4344,22 +4797,22 @@
       <c r="A80" t="s">
         <v>45</v>
       </c>
-      <c r="B80" s="15">
+      <c r="B80" s="13">
         <v>2019</v>
       </c>
       <c r="C80" s="2">
         <v>43527</v>
       </c>
-      <c r="D80" s="15" t="s">
+      <c r="D80" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="E80" s="6" t="s">
+      <c r="E80" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="F80" s="6" t="s">
+      <c r="F80" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="G80" s="6" t="s">
+      <c r="G80" s="5" t="s">
         <v>15</v>
       </c>
       <c r="H80" s="3">
@@ -4368,16 +4821,22 @@
       <c r="I80" s="3">
         <v>27.769863013698629</v>
       </c>
-      <c r="J80" s="7">
+      <c r="J80" s="6">
         <v>1</v>
       </c>
       <c r="K80">
         <v>0</v>
+      </c>
+      <c r="L80">
+        <v>9</v>
+      </c>
+      <c r="M80">
+        <v>3</v>
       </c>
       <c r="N80">
         <v>33</v>
       </c>
-      <c r="O80" s="26">
+      <c r="O80" s="24">
         <v>42.21</v>
       </c>
     </row>
@@ -4385,22 +4844,22 @@
       <c r="A81" t="s">
         <v>45</v>
       </c>
-      <c r="B81" s="15">
+      <c r="B81" s="13">
         <v>2019</v>
       </c>
       <c r="C81" s="2">
         <v>43527</v>
       </c>
-      <c r="D81" s="15" t="s">
+      <c r="D81" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="E81" s="6" t="s">
+      <c r="E81" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="F81" s="6" t="s">
+      <c r="F81" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="G81" s="6" t="s">
+      <c r="G81" s="5" t="s">
         <v>42</v>
       </c>
       <c r="H81" s="3">
@@ -4409,16 +4868,22 @@
       <c r="I81" s="3">
         <v>26.183561643835617</v>
       </c>
-      <c r="J81" s="7">
+      <c r="J81" s="6">
         <v>2</v>
       </c>
       <c r="K81">
         <v>0</v>
+      </c>
+      <c r="L81">
+        <v>9</v>
+      </c>
+      <c r="M81">
+        <v>4</v>
       </c>
       <c r="N81">
         <v>31</v>
       </c>
-      <c r="O81" s="26">
+      <c r="O81" s="24">
         <v>42.21</v>
       </c>
     </row>
@@ -4426,22 +4891,22 @@
       <c r="A82" t="s">
         <v>45</v>
       </c>
-      <c r="B82" s="15">
+      <c r="B82" s="13">
         <v>2019</v>
       </c>
       <c r="C82" s="2">
         <v>43527</v>
       </c>
-      <c r="D82" s="15" t="s">
+      <c r="D82" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="E82" s="6" t="s">
+      <c r="E82" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="F82" s="6" t="s">
+      <c r="F82" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="G82" s="6" t="s">
+      <c r="G82" s="5" t="s">
         <v>20</v>
       </c>
       <c r="H82" s="3">
@@ -4450,16 +4915,22 @@
       <c r="I82" s="3">
         <v>26.652054794520549</v>
       </c>
-      <c r="J82" s="7">
+      <c r="J82" s="6">
         <v>3</v>
       </c>
       <c r="K82">
         <v>0</v>
+      </c>
+      <c r="L82">
+        <v>6</v>
+      </c>
+      <c r="M82">
+        <v>2</v>
       </c>
       <c r="N82">
         <v>24</v>
       </c>
-      <c r="O82" s="26">
+      <c r="O82" s="24">
         <v>42.21</v>
       </c>
     </row>
@@ -4467,13 +4938,13 @@
       <c r="A83" t="s">
         <v>25</v>
       </c>
-      <c r="B83" s="15">
+      <c r="B83" s="13">
         <v>2019</v>
       </c>
       <c r="C83" s="2">
         <v>43492</v>
       </c>
-      <c r="D83" s="15" t="s">
+      <c r="D83" s="13" t="s">
         <v>14</v>
       </c>
       <c r="E83" s="1" t="s">
@@ -4491,16 +4962,22 @@
       <c r="I83" s="3">
         <v>27.673972602739727</v>
       </c>
-      <c r="J83" s="7">
+      <c r="J83" s="6">
         <v>1</v>
       </c>
-      <c r="K83" s="4">
-        <v>0</v>
+      <c r="K83">
+        <v>0</v>
+      </c>
+      <c r="L83">
+        <v>7</v>
+      </c>
+      <c r="M83">
+        <v>4</v>
       </c>
       <c r="N83">
         <v>29</v>
       </c>
-      <c r="O83" s="26">
+      <c r="O83" s="24">
         <v>51.688000000000002</v>
       </c>
     </row>
@@ -4508,13 +4985,13 @@
       <c r="A84" t="s">
         <v>25</v>
       </c>
-      <c r="B84" s="15">
+      <c r="B84" s="13">
         <v>2019</v>
       </c>
       <c r="C84" s="2">
         <v>43492</v>
       </c>
-      <c r="D84" s="15" t="s">
+      <c r="D84" s="13" t="s">
         <v>14</v>
       </c>
       <c r="E84" s="1" t="s">
@@ -4532,16 +5009,22 @@
       <c r="I84" s="3">
         <v>28.890410958904109</v>
       </c>
-      <c r="J84" s="7">
+      <c r="J84" s="6">
         <v>2</v>
       </c>
       <c r="K84">
         <v>0</v>
+      </c>
+      <c r="L84">
+        <v>8</v>
+      </c>
+      <c r="M84">
+        <v>1</v>
       </c>
       <c r="N84">
         <v>24</v>
       </c>
-      <c r="O84" s="26">
+      <c r="O84" s="24">
         <v>51.688000000000002</v>
       </c>
     </row>
@@ -4549,13 +5032,13 @@
       <c r="A85" t="s">
         <v>25</v>
       </c>
-      <c r="B85" s="15">
+      <c r="B85" s="13">
         <v>2019</v>
       </c>
       <c r="C85" s="2">
         <v>43492</v>
       </c>
-      <c r="D85" s="15" t="s">
+      <c r="D85" s="13" t="s">
         <v>14</v>
       </c>
       <c r="E85" s="1" t="s">
@@ -4573,16 +5056,22 @@
       <c r="I85" s="3">
         <v>25.843835616438355</v>
       </c>
-      <c r="J85" s="7">
-        <v>3</v>
-      </c>
-      <c r="K85" s="4">
-        <v>0</v>
+      <c r="J85" s="6">
+        <v>3</v>
+      </c>
+      <c r="K85">
+        <v>0</v>
+      </c>
+      <c r="L85">
+        <v>4</v>
+      </c>
+      <c r="M85">
+        <v>1</v>
       </c>
       <c r="N85">
         <v>12</v>
       </c>
-      <c r="O85" s="26">
+      <c r="O85" s="24">
         <v>51.688000000000002</v>
       </c>
     </row>
@@ -4618,46 +5107,46 @@
       <formula>#REF!="Q"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J65">
+    <cfRule type="cellIs" dxfId="8" priority="1" operator="between">
+      <formula>0</formula>
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="K68:K70">
-    <cfRule type="cellIs" dxfId="8" priority="19" operator="between">
+    <cfRule type="cellIs" dxfId="7" priority="19" operator="between">
       <formula>1</formula>
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="20" operator="between">
+    <cfRule type="cellIs" dxfId="6" priority="20" operator="between">
       <formula>2</formula>
       <formula>2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="21" operator="between">
+    <cfRule type="cellIs" dxfId="5" priority="21" operator="between">
       <formula>3</formula>
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="22" operator="between">
+    <cfRule type="cellIs" dxfId="4" priority="22" operator="between">
       <formula>5</formula>
       <formula>5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N68:N70">
-    <cfRule type="cellIs" dxfId="4" priority="23" operator="between">
+    <cfRule type="cellIs" dxfId="3" priority="23" operator="between">
       <formula>2</formula>
       <formula>2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="24" operator="between">
+    <cfRule type="cellIs" dxfId="2" priority="24" operator="between">
       <formula>4</formula>
       <formula>4</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="25" operator="between">
+    <cfRule type="cellIs" dxfId="1" priority="25" operator="between">
       <formula>6</formula>
       <formula>6</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="26" operator="between">
+    <cfRule type="cellIs" dxfId="0" priority="26" operator="between">
       <formula>10</formula>
       <formula>10</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J65">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="between">
-      <formula>0</formula>
-      <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/pages/WR_progressions/Womens_Madison.xlsx
+++ b/pages/WR_progressions/Womens_Madison.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\WR_progressions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C0CF36B-ACE3-4F2C-975A-A570E04A121D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8826A847-843E-42C5-8A95-B45EB031A32C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{8F2B8F41-998D-4BB8-BE11-A97939F5BC1E}"/>
+    <workbookView xWindow="38280" yWindow="30" windowWidth="29040" windowHeight="15720" xr2:uid="{8F2B8F41-998D-4BB8-BE11-A97939F5BC1E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$O$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$O$91</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="134">
   <si>
     <t>Location</t>
   </si>
@@ -448,6 +448,21 @@
   </si>
   <si>
     <t>CONFALONIERI Maria Giulia</t>
+  </si>
+  <si>
+    <t>Nilai</t>
+  </si>
+  <si>
+    <t>WIEBES Lorena</t>
+  </si>
+  <si>
+    <t>FOWLER Prudence</t>
+  </si>
+  <si>
+    <t>BOOTHMAN Erin</t>
+  </si>
+  <si>
+    <t>VEENHOVEN Nienke</t>
   </si>
 </sst>
 </file>
@@ -589,7 +604,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -625,11 +640,32 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="21">
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1077,13 +1113,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{856B23EE-F0D3-4856-AD89-ACB67D64024E}">
-  <dimension ref="A1:O85"/>
+  <dimension ref="A1:O91"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="28" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="22.3984375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.73046875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.59765625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.73046875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.45">
@@ -1134,345 +1173,345 @@
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A2" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="B2" s="18">
-        <v>2025</v>
-      </c>
-      <c r="C2" s="2">
-        <v>45952</v>
-      </c>
-      <c r="D2" s="18" t="s">
-        <v>18</v>
+      <c r="A2" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="B2" s="7">
+        <v>2026</v>
+      </c>
+      <c r="C2" s="8">
+        <v>46136</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>14</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>50</v>
+        <v>130</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="H2" s="23">
-        <v>22.484931506849314</v>
-      </c>
-      <c r="I2" s="23">
-        <v>31.635616438356163</v>
-      </c>
-      <c r="J2" s="22">
+        <v>15</v>
+      </c>
+      <c r="H2" s="25">
+        <v>22.246575342465754</v>
+      </c>
+      <c r="I2" s="25">
+        <v>27.123287671232877</v>
+      </c>
+      <c r="J2" s="7">
         <v>1</v>
       </c>
-      <c r="K2" s="18">
-        <v>0</v>
-      </c>
-      <c r="L2" s="18">
+      <c r="K2" s="7">
+        <v>20</v>
+      </c>
+      <c r="L2">
+        <v>9</v>
+      </c>
+      <c r="M2">
+        <v>6</v>
+      </c>
+      <c r="N2" s="7">
+        <v>66</v>
+      </c>
+      <c r="O2" s="22">
+        <v>53.704999999999998</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A3" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="B3" s="7">
+        <v>2026</v>
+      </c>
+      <c r="C3" s="8">
+        <v>46136</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3" s="25">
+        <v>28.487671232876714</v>
+      </c>
+      <c r="I3" s="25">
+        <v>23.293150684931508</v>
+      </c>
+      <c r="J3" s="7">
+        <v>2</v>
+      </c>
+      <c r="K3" s="7">
+        <v>20</v>
+      </c>
+      <c r="L3">
         <v>8</v>
       </c>
-      <c r="M2" s="18">
-        <v>2</v>
-      </c>
-      <c r="N2" s="18">
+      <c r="M3">
+        <v>4</v>
+      </c>
+      <c r="N3" s="7">
+        <v>54</v>
+      </c>
+      <c r="O3" s="22">
+        <v>53.704999999999998</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A4" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="B4" s="7">
+        <v>2026</v>
+      </c>
+      <c r="C4" s="8">
+        <v>46136</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="H4" s="25">
+        <v>29.2</v>
+      </c>
+      <c r="I4" s="25">
+        <v>28.931506849315067</v>
+      </c>
+      <c r="J4" s="7">
+        <v>3</v>
+      </c>
+      <c r="K4" s="7">
+        <v>20</v>
+      </c>
+      <c r="L4">
+        <v>7</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+      <c r="N4" s="7">
+        <v>37</v>
+      </c>
+      <c r="O4" s="22">
+        <v>53.704999999999998</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A5" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="7">
+        <v>2026</v>
+      </c>
+      <c r="C5" s="8">
+        <v>46129</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="G5" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="O2" s="18">
-        <v>54.573</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A3" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="B3" s="18">
-        <v>2025</v>
-      </c>
-      <c r="C3" s="2">
-        <v>45952</v>
-      </c>
-      <c r="D3" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="H3" s="23">
-        <v>25.2</v>
-      </c>
-      <c r="I3" s="23">
-        <v>27.92876712328767</v>
-      </c>
-      <c r="J3" s="22">
-        <v>2</v>
-      </c>
-      <c r="K3" s="18">
-        <v>0</v>
-      </c>
-      <c r="L3" s="18">
-        <v>8</v>
-      </c>
-      <c r="M3" s="18">
-        <v>3</v>
-      </c>
-      <c r="N3" s="18">
-        <v>24</v>
-      </c>
-      <c r="O3" s="18">
-        <v>54.573</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A4" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="B4" s="18">
-        <v>2025</v>
-      </c>
-      <c r="C4" s="2">
-        <v>45952</v>
-      </c>
-      <c r="D4" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H4" s="23">
-        <v>26.347945205479451</v>
-      </c>
-      <c r="I4" s="23">
-        <v>24.838356164383562</v>
-      </c>
-      <c r="J4" s="22">
-        <v>3</v>
-      </c>
-      <c r="K4" s="18">
-        <v>0</v>
-      </c>
-      <c r="L4" s="18">
+      <c r="H5" s="25">
+        <v>28.413698630136988</v>
+      </c>
+      <c r="I5" s="25">
+        <v>27</v>
+      </c>
+      <c r="J5" s="7">
+        <v>1</v>
+      </c>
+      <c r="K5" s="7">
+        <v>20</v>
+      </c>
+      <c r="L5">
         <v>7</v>
-      </c>
-      <c r="M4" s="18">
-        <v>1</v>
-      </c>
-      <c r="N4" s="18">
-        <v>20</v>
-      </c>
-      <c r="O4" s="18">
-        <v>54.573</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="1">
-        <v>2025</v>
-      </c>
-      <c r="C5" s="2">
-        <v>45730</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="H5" s="3">
-        <v>28.824657534246576</v>
-      </c>
-      <c r="I5" s="3">
-        <v>24.216438356164385</v>
-      </c>
-      <c r="J5" s="22">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>20</v>
-      </c>
-      <c r="L5">
-        <v>9</v>
       </c>
       <c r="M5">
         <v>4</v>
       </c>
-      <c r="N5">
-        <v>53</v>
-      </c>
-      <c r="O5" s="4">
-        <v>54.107999999999997</v>
+      <c r="N5" s="7">
+        <v>47</v>
+      </c>
+      <c r="O5" s="22">
+        <v>55.527000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="1">
+      <c r="A6" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="7">
+        <v>2026</v>
+      </c>
+      <c r="C6" s="8">
+        <v>46129</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" s="25">
+        <v>18.994520547945207</v>
+      </c>
+      <c r="I6" s="25">
+        <v>22.969863013698632</v>
+      </c>
+      <c r="J6" s="7">
+        <v>2</v>
+      </c>
+      <c r="K6" s="7">
+        <v>20</v>
+      </c>
+      <c r="L6">
+        <v>5</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
+      </c>
+      <c r="N6" s="7">
+        <v>40</v>
+      </c>
+      <c r="O6" s="22">
+        <v>55.527000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A7" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="7">
+        <v>2026</v>
+      </c>
+      <c r="C7" s="8">
+        <v>46129</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" s="25">
+        <v>22.227397260273971</v>
+      </c>
+      <c r="I7" s="25">
+        <v>22.090410958904108</v>
+      </c>
+      <c r="J7" s="7">
+        <v>3</v>
+      </c>
+      <c r="K7" s="7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>8</v>
+      </c>
+      <c r="M7">
+        <v>2</v>
+      </c>
+      <c r="N7" s="7">
+        <v>28</v>
+      </c>
+      <c r="O7" s="22">
+        <v>55.527000000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A8" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" s="18">
         <v>2025</v>
       </c>
-      <c r="C6" s="2">
-        <v>45730</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="H6" s="3">
-        <v>18.36986301369863</v>
-      </c>
-      <c r="I6" s="3">
-        <v>25.717808219178082</v>
-      </c>
-      <c r="J6" s="22">
-        <v>2</v>
-      </c>
-      <c r="K6">
-        <v>20</v>
-      </c>
-      <c r="L6">
-        <v>8</v>
-      </c>
-      <c r="M6">
-        <v>1</v>
-      </c>
-      <c r="N6">
-        <v>43</v>
-      </c>
-      <c r="O6" s="4">
-        <v>54.107999999999997</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="1">
-        <v>2025</v>
-      </c>
-      <c r="C7" s="2">
-        <v>45730</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="H7" s="3">
-        <v>23.265753424657536</v>
-      </c>
-      <c r="I7" s="3">
-        <v>26.07123287671233</v>
-      </c>
-      <c r="J7" s="22">
-        <v>3</v>
-      </c>
-      <c r="K7">
-        <v>20</v>
-      </c>
-      <c r="L7">
-        <v>7</v>
-      </c>
-      <c r="M7">
-        <v>3</v>
-      </c>
-      <c r="N7">
-        <v>43</v>
-      </c>
-      <c r="O7" s="4">
-        <v>54.107999999999997</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8">
-        <v>2024</v>
-      </c>
       <c r="C8" s="2">
-        <v>45585</v>
-      </c>
-      <c r="D8" t="s">
+        <v>45952</v>
+      </c>
+      <c r="D8" s="18" t="s">
         <v>18</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="H8" s="3">
-        <v>28.424657534246574</v>
-      </c>
-      <c r="I8" s="3">
-        <v>32.290410958904111</v>
+        <v>28</v>
+      </c>
+      <c r="H8" s="23">
+        <v>22.484931506849314</v>
+      </c>
+      <c r="I8" s="23">
+        <v>31.635616438356163</v>
       </c>
       <c r="J8" s="22">
         <v>1</v>
       </c>
-      <c r="K8">
-        <v>20</v>
-      </c>
-      <c r="L8">
-        <v>9</v>
-      </c>
-      <c r="M8">
-        <v>3</v>
-      </c>
-      <c r="N8">
-        <v>46</v>
-      </c>
-      <c r="O8">
-        <v>54.683999999999997</v>
+      <c r="K8" s="18">
+        <v>0</v>
+      </c>
+      <c r="L8" s="18">
+        <v>8</v>
+      </c>
+      <c r="M8" s="18">
+        <v>2</v>
+      </c>
+      <c r="N8" s="18">
+        <v>30</v>
+      </c>
+      <c r="O8" s="18">
+        <v>54.573</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9">
-        <v>2024</v>
+      <c r="A9" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="B9" s="18">
+        <v>2025</v>
       </c>
       <c r="C9" s="2">
-        <v>45585</v>
-      </c>
-      <c r="D9" t="s">
+        <v>45952</v>
+      </c>
+      <c r="D9" s="18" t="s">
         <v>18</v>
       </c>
       <c r="E9" s="7" t="s">
@@ -1484,105 +1523,105 @@
       <c r="G9" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="H9" s="3">
-        <v>24.19178082191781</v>
-      </c>
-      <c r="I9" s="3">
-        <v>26.920547945205481</v>
+      <c r="H9" s="23">
+        <v>25.2</v>
+      </c>
+      <c r="I9" s="23">
+        <v>27.92876712328767</v>
       </c>
       <c r="J9" s="22">
         <v>2</v>
       </c>
-      <c r="K9">
-        <v>20</v>
-      </c>
-      <c r="L9">
+      <c r="K9" s="18">
+        <v>0</v>
+      </c>
+      <c r="L9" s="18">
         <v>8</v>
       </c>
-      <c r="M9">
-        <v>1</v>
-      </c>
-      <c r="N9">
-        <v>43</v>
-      </c>
-      <c r="O9">
-        <v>54.683999999999997</v>
+      <c r="M9" s="18">
+        <v>3</v>
+      </c>
+      <c r="N9" s="18">
+        <v>24</v>
+      </c>
+      <c r="O9" s="18">
+        <v>54.573</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10">
-        <v>2024</v>
+      <c r="A10" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="B10" s="18">
+        <v>2025</v>
       </c>
       <c r="C10" s="2">
-        <v>45585</v>
-      </c>
-      <c r="D10" t="s">
+        <v>45952</v>
+      </c>
+      <c r="D10" s="18" t="s">
         <v>18</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="H10" s="3">
-        <v>34.241095890410961</v>
-      </c>
-      <c r="I10" s="3">
-        <v>30.627397260273973</v>
+        <v>23</v>
+      </c>
+      <c r="H10" s="23">
+        <v>26.347945205479451</v>
+      </c>
+      <c r="I10" s="23">
+        <v>24.838356164383562</v>
       </c>
       <c r="J10" s="22">
         <v>3</v>
       </c>
-      <c r="K10">
-        <v>0</v>
-      </c>
-      <c r="L10">
-        <v>10</v>
-      </c>
-      <c r="M10">
-        <v>5</v>
-      </c>
-      <c r="N10">
-        <v>42</v>
-      </c>
-      <c r="O10">
-        <v>54.683999999999997</v>
+      <c r="K10" s="18">
+        <v>0</v>
+      </c>
+      <c r="L10" s="18">
+        <v>7</v>
+      </c>
+      <c r="M10" s="18">
+        <v>1</v>
+      </c>
+      <c r="N10" s="18">
+        <v>20</v>
+      </c>
+      <c r="O10" s="18">
+        <v>54.573</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B11" s="1">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C11" s="2">
-        <v>45514</v>
+        <v>45730</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H11" s="3">
-        <v>25.227397260273971</v>
+        <v>28.824657534246576</v>
       </c>
       <c r="I11" s="3">
-        <v>23.717808219178082</v>
+        <v>24.216438356164385</v>
       </c>
       <c r="J11" s="22">
         <v>1</v>
@@ -1591,92 +1630,92 @@
         <v>20</v>
       </c>
       <c r="L11">
+        <v>9</v>
+      </c>
+      <c r="M11">
         <v>4</v>
       </c>
-      <c r="M11">
-        <v>3</v>
-      </c>
       <c r="N11">
-        <v>37</v>
-      </c>
-      <c r="O11">
-        <v>54.962000000000003</v>
+        <v>53</v>
+      </c>
+      <c r="O11" s="4">
+        <v>54.107999999999997</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A12" s="1" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B12" s="1">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C12" s="2">
-        <v>45514</v>
+        <v>45730</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="H12" s="3">
-        <v>30.024657534246575</v>
+        <v>18.36986301369863</v>
       </c>
       <c r="I12" s="3">
-        <v>34.128767123287673</v>
+        <v>25.717808219178082</v>
       </c>
       <c r="J12" s="22">
         <v>2</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L12">
         <v>8</v>
       </c>
       <c r="M12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N12">
-        <v>31</v>
-      </c>
-      <c r="O12">
-        <v>54.962000000000003</v>
+        <v>43</v>
+      </c>
+      <c r="O12" s="4">
+        <v>54.107999999999997</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A13" s="1" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B13" s="1">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C13" s="2">
-        <v>45514</v>
+        <v>45730</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="H13" s="3">
-        <v>23.005479452054793</v>
+        <v>23.265753424657536</v>
       </c>
       <c r="I13" s="3">
-        <v>20.621917808219177</v>
+        <v>26.07123287671233</v>
       </c>
       <c r="J13" s="22">
         <v>3</v>
@@ -1685,80 +1724,80 @@
         <v>20</v>
       </c>
       <c r="L13">
+        <v>7</v>
+      </c>
+      <c r="M13">
         <v>3</v>
       </c>
-      <c r="M13">
-        <v>1</v>
-      </c>
       <c r="N13">
-        <v>28</v>
-      </c>
-      <c r="O13">
-        <v>54.962000000000003</v>
+        <v>43</v>
+      </c>
+      <c r="O13" s="4">
+        <v>54.107999999999997</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="B14">
         <v>2024</v>
       </c>
       <c r="C14" s="2">
-        <v>45396</v>
+        <v>45585</v>
       </c>
       <c r="D14" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H14" s="3">
-        <v>30.109589041095891</v>
+        <v>28.424657534246574</v>
       </c>
       <c r="I14" s="3">
-        <v>33.723287671232875</v>
-      </c>
-      <c r="J14" s="7">
+        <v>32.290410958904111</v>
+      </c>
+      <c r="J14" s="22">
         <v>1</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L14">
         <v>9</v>
       </c>
       <c r="M14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N14">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="O14">
-        <v>52.811999999999998</v>
+        <v>54.683999999999997</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="B15">
         <v>2024</v>
       </c>
       <c r="C15" s="2">
-        <v>45396</v>
+        <v>45585</v>
       </c>
       <c r="D15" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="F15" s="7" t="s">
         <v>52</v>
@@ -1767,323 +1806,323 @@
         <v>30</v>
       </c>
       <c r="H15" s="3">
-        <v>24.989041095890411</v>
+        <v>24.19178082191781</v>
       </c>
       <c r="I15" s="3">
-        <v>26.402739726027399</v>
-      </c>
-      <c r="J15" s="7">
+        <v>26.920547945205481</v>
+      </c>
+      <c r="J15" s="22">
         <v>2</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N15">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="O15">
-        <v>52.811999999999998</v>
+        <v>54.683999999999997</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="B16">
         <v>2024</v>
       </c>
       <c r="C16" s="2">
-        <v>45396</v>
+        <v>45585</v>
       </c>
       <c r="D16" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>69</v>
+        <v>28</v>
       </c>
       <c r="H16" s="3">
-        <v>29.323287671232876</v>
+        <v>34.241095890410961</v>
       </c>
       <c r="I16" s="3">
-        <v>29.824657534246576</v>
-      </c>
-      <c r="J16" s="7">
+        <v>30.627397260273973</v>
+      </c>
+      <c r="J16" s="22">
         <v>3</v>
       </c>
       <c r="K16">
         <v>0</v>
       </c>
       <c r="L16">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M16">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N16">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="O16">
-        <v>52.811999999999998</v>
+        <v>54.683999999999997</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A17" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B17" s="1">
         <v>2024</v>
       </c>
       <c r="C17" s="2">
-        <v>45368</v>
-      </c>
-      <c r="D17" t="s">
-        <v>14</v>
+        <v>45514</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>72</v>
+        <v>23</v>
       </c>
       <c r="H17" s="3">
-        <v>19.265753424657536</v>
+        <v>25.227397260273971</v>
       </c>
       <c r="I17" s="3">
-        <v>22.186301369863013</v>
-      </c>
-      <c r="J17" s="7">
+        <v>23.717808219178082</v>
+      </c>
+      <c r="J17" s="22">
         <v>1</v>
       </c>
       <c r="K17">
         <v>20</v>
       </c>
       <c r="L17">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M17">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N17">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="O17">
-        <v>53.307000000000002</v>
+        <v>54.962000000000003</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A18" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B18" s="1">
         <v>2024</v>
       </c>
       <c r="C18" s="2">
-        <v>45368</v>
-      </c>
-      <c r="D18" t="s">
-        <v>14</v>
+        <v>45514</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H18" s="3">
-        <v>26.38082191780822</v>
+        <v>30.024657534246575</v>
       </c>
       <c r="I18" s="3">
-        <v>25.076712328767123</v>
-      </c>
-      <c r="J18" s="7">
+        <v>34.128767123287673</v>
+      </c>
+      <c r="J18" s="22">
         <v>2</v>
       </c>
       <c r="K18">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="L18">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N18">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="O18">
-        <v>53.307000000000002</v>
+        <v>54.962000000000003</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A19" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B19" s="1">
         <v>2024</v>
       </c>
       <c r="C19" s="2">
-        <v>45368</v>
-      </c>
-      <c r="D19" t="s">
-        <v>14</v>
+        <v>45514</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="G19" s="7" t="s">
         <v>15</v>
       </c>
       <c r="H19" s="3">
-        <v>24.805479452054794</v>
+        <v>23.005479452054793</v>
       </c>
       <c r="I19" s="3">
-        <v>20.139726027397259</v>
-      </c>
-      <c r="J19" s="7">
+        <v>20.621917808219177</v>
+      </c>
+      <c r="J19" s="22">
         <v>3</v>
       </c>
       <c r="K19">
         <v>20</v>
       </c>
       <c r="L19">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N19">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="O19">
-        <v>53.307000000000002</v>
+        <v>54.962000000000003</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A20" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B20" s="1">
+      <c r="A20" t="s">
+        <v>24</v>
+      </c>
+      <c r="B20">
         <v>2024</v>
       </c>
       <c r="C20" s="2">
-        <v>45326</v>
-      </c>
-      <c r="D20" s="1" t="s">
+        <v>45396</v>
+      </c>
+      <c r="D20" t="s">
         <v>14</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>50</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G20" s="7" t="s">
         <v>28</v>
       </c>
       <c r="H20" s="3">
-        <v>29.917808219178081</v>
+        <v>30.109589041095891</v>
       </c>
       <c r="I20" s="3">
-        <v>29.427397260273974</v>
-      </c>
-      <c r="J20" s="22">
+        <v>33.723287671232875</v>
+      </c>
+      <c r="J20" s="7">
         <v>1</v>
       </c>
       <c r="K20">
         <v>0</v>
       </c>
       <c r="L20">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M20">
         <v>5</v>
       </c>
       <c r="N20">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="O20">
-        <v>52.631999999999998</v>
+        <v>52.811999999999998</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A21" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B21" s="1">
+      <c r="A21" t="s">
+        <v>24</v>
+      </c>
+      <c r="B21">
         <v>2024</v>
       </c>
       <c r="C21" s="2">
-        <v>45326</v>
-      </c>
-      <c r="D21" s="1" t="s">
+        <v>45396</v>
+      </c>
+      <c r="D21" t="s">
         <v>14</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="H21" s="3">
-        <v>29.389041095890413</v>
+        <v>24.989041095890411</v>
       </c>
       <c r="I21" s="3">
-        <v>27.950684931506849</v>
-      </c>
-      <c r="J21" s="22">
+        <v>26.402739726027399</v>
+      </c>
+      <c r="J21" s="7">
         <v>2</v>
       </c>
       <c r="K21">
         <v>0</v>
       </c>
       <c r="L21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N21">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="O21">
-        <v>52.631999999999998</v>
+        <v>52.811999999999998</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A22" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B22" s="1">
+      <c r="A22" t="s">
+        <v>24</v>
+      </c>
+      <c r="B22">
         <v>2024</v>
       </c>
       <c r="C22" s="2">
-        <v>45326</v>
-      </c>
-      <c r="D22" s="1" t="s">
+        <v>45396</v>
+      </c>
+      <c r="D22" t="s">
         <v>14</v>
       </c>
       <c r="E22" s="7" t="s">
@@ -2096,341 +2135,341 @@
         <v>69</v>
       </c>
       <c r="H22" s="3">
-        <v>29.13150684931507</v>
+        <v>29.323287671232876</v>
       </c>
       <c r="I22" s="3">
-        <v>29.632876712328766</v>
-      </c>
-      <c r="J22" s="22">
+        <v>29.824657534246576</v>
+      </c>
+      <c r="J22" s="7">
         <v>3</v>
       </c>
       <c r="K22">
         <v>0</v>
       </c>
       <c r="L22">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M22">
         <v>2</v>
       </c>
       <c r="N22">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="O22">
-        <v>52.631999999999998</v>
+        <v>52.811999999999998</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A23" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="B23" s="15">
-        <v>2023</v>
+      <c r="A23" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B23" s="1">
+        <v>2024</v>
       </c>
       <c r="C23" s="2">
-        <v>45146</v>
-      </c>
-      <c r="D23" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="E23" s="7" t="s" cm="1">
-        <v>62</v>
+        <v>45368</v>
+      </c>
+      <c r="D23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>70</v>
       </c>
       <c r="F23" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="H23" s="3">
+        <v>19.265753424657536</v>
+      </c>
+      <c r="I23" s="3">
+        <v>22.186301369863013</v>
+      </c>
+      <c r="J23" s="7">
+        <v>1</v>
+      </c>
+      <c r="K23">
+        <v>20</v>
+      </c>
+      <c r="L23">
+        <v>7</v>
+      </c>
+      <c r="M23">
+        <v>4</v>
+      </c>
+      <c r="N23">
+        <v>54</v>
+      </c>
+      <c r="O23">
+        <v>53.307000000000002</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A24" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B24" s="1">
+        <v>2024</v>
+      </c>
+      <c r="C24" s="2">
+        <v>45368</v>
+      </c>
+      <c r="D24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H24" s="3">
+        <v>26.38082191780822</v>
+      </c>
+      <c r="I24" s="3">
+        <v>25.076712328767123</v>
+      </c>
+      <c r="J24" s="7">
+        <v>2</v>
+      </c>
+      <c r="K24">
+        <v>20</v>
+      </c>
+      <c r="L24">
+        <v>10</v>
+      </c>
+      <c r="M24">
+        <v>4</v>
+      </c>
+      <c r="N24">
+        <v>53</v>
+      </c>
+      <c r="O24">
+        <v>53.307000000000002</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A25" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" s="1">
+        <v>2024</v>
+      </c>
+      <c r="C25" s="2">
+        <v>45368</v>
+      </c>
+      <c r="D25" t="s">
+        <v>14</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H25" s="3">
+        <v>24.805479452054794</v>
+      </c>
+      <c r="I25" s="3">
+        <v>20.139726027397259</v>
+      </c>
+      <c r="J25" s="7">
+        <v>3</v>
+      </c>
+      <c r="K25">
+        <v>20</v>
+      </c>
+      <c r="L25">
+        <v>7</v>
+      </c>
+      <c r="M25">
+        <v>3</v>
+      </c>
+      <c r="N25">
+        <v>49</v>
+      </c>
+      <c r="O25">
+        <v>53.307000000000002</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A26" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B26" s="1">
+        <v>2024</v>
+      </c>
+      <c r="C26" s="2">
+        <v>45326</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="F26" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="G23" s="7" t="s">
+      <c r="G26" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="H23" s="3">
-        <v>33.030136986301372</v>
-      </c>
-      <c r="I23" s="3">
-        <v>28.926027397260274</v>
-      </c>
-      <c r="J23" s="22">
-        <v>1</v>
-      </c>
-      <c r="K23">
-        <v>0</v>
-      </c>
-      <c r="L23">
-        <v>10</v>
-      </c>
-      <c r="M23">
-        <v>3</v>
-      </c>
-      <c r="N23">
-        <v>28</v>
-      </c>
-      <c r="O23">
-        <v>50.07</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A24" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="B24" s="15">
-        <v>2023</v>
-      </c>
-      <c r="C24" s="2">
-        <v>45146</v>
-      </c>
-      <c r="D24" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="E24" s="7" t="s" cm="1">
-        <v>76</v>
-      </c>
-      <c r="F24" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="G24" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="H24" s="3">
-        <v>28.887671232876713</v>
-      </c>
-      <c r="I24" s="3">
-        <v>27.449315068493149</v>
-      </c>
-      <c r="J24" s="22">
-        <v>2</v>
-      </c>
-      <c r="K24">
-        <v>0</v>
-      </c>
-      <c r="L24">
-        <v>7</v>
-      </c>
-      <c r="M24">
-        <v>1</v>
-      </c>
-      <c r="N24">
-        <v>25</v>
-      </c>
-      <c r="O24">
-        <v>50.07</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A25" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="B25" s="15">
-        <v>2023</v>
-      </c>
-      <c r="C25" s="2">
-        <v>45146</v>
-      </c>
-      <c r="D25" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="E25" s="7" t="s" cm="1">
-        <v>51</v>
-      </c>
-      <c r="F25" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="G25" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="H25" s="3">
-        <v>22.980821917808218</v>
-      </c>
-      <c r="I25" s="3">
-        <v>24.575342465753426</v>
-      </c>
-      <c r="J25" s="22">
-        <v>3</v>
-      </c>
-      <c r="K25">
-        <v>0</v>
-      </c>
-      <c r="L25">
-        <v>6</v>
-      </c>
-      <c r="M25">
-        <v>2</v>
-      </c>
-      <c r="N25">
-        <v>22</v>
-      </c>
-      <c r="O25">
-        <v>50.07</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A26" t="s">
-        <v>24</v>
-      </c>
-      <c r="B26">
-        <v>2023</v>
-      </c>
-      <c r="C26" s="2">
-        <v>45039</v>
-      </c>
-      <c r="D26" t="s">
-        <v>14</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="F26" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="G26" s="7" t="s">
-        <v>16</v>
-      </c>
       <c r="H26" s="3">
-        <v>22.638356164383563</v>
+        <v>29.917808219178081</v>
       </c>
       <c r="I26" s="3">
-        <v>27.463013698630139</v>
+        <v>29.427397260273974</v>
       </c>
       <c r="J26" s="22">
         <v>1</v>
       </c>
       <c r="K26">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="L26">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M26">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N26">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="O26">
-        <v>50.68</v>
+        <v>52.631999999999998</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A27" t="s">
-        <v>24</v>
-      </c>
-      <c r="B27">
-        <v>2023</v>
+      <c r="A27" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27" s="1">
+        <v>2024</v>
       </c>
       <c r="C27" s="2">
-        <v>45039</v>
-      </c>
-      <c r="D27" t="s">
+        <v>45326</v>
+      </c>
+      <c r="D27" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="H27" s="3">
-        <v>29.12876712328767</v>
+        <v>29.389041095890413</v>
       </c>
       <c r="I27" s="3">
-        <v>32.742465753424661</v>
+        <v>27.950684931506849</v>
       </c>
       <c r="J27" s="22">
         <v>2</v>
       </c>
       <c r="K27">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="L27">
         <v>8</v>
       </c>
       <c r="M27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N27">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="O27">
-        <v>50.68</v>
+        <v>52.631999999999998</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A28" t="s">
-        <v>24</v>
-      </c>
-      <c r="B28">
-        <v>2023</v>
+      <c r="A28" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" s="1">
+        <v>2024</v>
       </c>
       <c r="C28" s="2">
-        <v>45039</v>
-      </c>
-      <c r="D28" t="s">
+        <v>45326</v>
+      </c>
+      <c r="D28" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="H28" s="3">
-        <v>25.161643835616438</v>
+        <v>29.13150684931507</v>
       </c>
       <c r="I28" s="3">
-        <v>23.473972602739725</v>
+        <v>29.632876712328766</v>
       </c>
       <c r="J28" s="22">
         <v>3</v>
       </c>
       <c r="K28">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="L28">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N28">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="O28">
-        <v>50.68</v>
+        <v>52.631999999999998</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A29" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B29" s="1">
+      <c r="A29" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B29" s="15">
         <v>2023</v>
       </c>
-      <c r="C29" s="16">
-        <v>45002</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E29" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="F29" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="G29" s="11" t="s">
-        <v>30</v>
+      <c r="C29" s="2">
+        <v>45146</v>
+      </c>
+      <c r="D29" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="E29" s="7" t="s" cm="1">
+        <v>62</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>28</v>
       </c>
       <c r="H29" s="3">
-        <v>24.186301369863013</v>
+        <v>33.030136986301372</v>
       </c>
       <c r="I29" s="3">
-        <v>23.906849315068492</v>
-      </c>
-      <c r="J29" s="11">
+        <v>28.926027397260274</v>
+      </c>
+      <c r="J29" s="22">
         <v>1</v>
       </c>
       <c r="K29">
@@ -2440,136 +2479,136 @@
         <v>10</v>
       </c>
       <c r="M29">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N29">
-        <v>35</v>
-      </c>
-      <c r="O29" s="6">
-        <v>50.966999999999999</v>
+        <v>28</v>
+      </c>
+      <c r="O29">
+        <v>50.07</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A30" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B30" s="1">
+      <c r="A30" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B30" s="15">
         <v>2023</v>
       </c>
-      <c r="C30" s="16">
-        <v>45002</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E30" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="F30" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="G30" s="11" t="s">
-        <v>20</v>
+      <c r="C30" s="2">
+        <v>45146</v>
+      </c>
+      <c r="D30" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="E30" s="7" t="s" cm="1">
+        <v>76</v>
+      </c>
+      <c r="F30" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="G30" s="7" t="s">
+        <v>42</v>
       </c>
       <c r="H30" s="3">
-        <v>26.824657534246576</v>
+        <v>28.887671232876713</v>
       </c>
       <c r="I30" s="3">
-        <v>30.69041095890411</v>
-      </c>
-      <c r="J30" s="11">
+        <v>27.449315068493149</v>
+      </c>
+      <c r="J30" s="22">
         <v>2</v>
       </c>
       <c r="K30">
         <v>0</v>
       </c>
       <c r="L30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M30">
+        <v>1</v>
+      </c>
+      <c r="N30">
+        <v>25</v>
+      </c>
+      <c r="O30">
+        <v>50.07</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A31" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B31" s="15">
+        <v>2023</v>
+      </c>
+      <c r="C31" s="2">
+        <v>45146</v>
+      </c>
+      <c r="D31" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="E31" s="7" t="s" cm="1">
+        <v>51</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G31" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H31" s="3">
+        <v>22.980821917808218</v>
+      </c>
+      <c r="I31" s="3">
+        <v>24.575342465753426</v>
+      </c>
+      <c r="J31" s="22">
         <v>3</v>
       </c>
-      <c r="N30">
-        <v>34</v>
-      </c>
-      <c r="O30" s="6">
-        <v>50.966999999999999</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A31" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B31" s="1">
-        <v>2023</v>
-      </c>
-      <c r="C31" s="16">
-        <v>45002</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E31" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="F31" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="G31" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="H31" s="3">
-        <v>25.375342465753423</v>
-      </c>
-      <c r="I31" s="3">
-        <v>22.205479452054796</v>
-      </c>
-      <c r="J31" s="11">
-        <v>3</v>
-      </c>
       <c r="K31">
         <v>0</v>
       </c>
       <c r="L31">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M31">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N31">
-        <v>24</v>
-      </c>
-      <c r="O31" s="6">
-        <v>50.966999999999999</v>
+        <v>22</v>
+      </c>
+      <c r="O31">
+        <v>50.07</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B32">
         <v>2023</v>
       </c>
       <c r="C32" s="2">
-        <v>44983</v>
+        <v>45039</v>
       </c>
       <c r="D32" t="s">
         <v>14</v>
       </c>
-      <c r="E32" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="F32" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="G32" s="19" t="s">
-        <v>20</v>
+      <c r="E32" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="F32" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="G32" s="7" t="s">
+        <v>16</v>
       </c>
       <c r="H32" s="3">
-        <v>26.775342465753425</v>
+        <v>22.638356164383563</v>
       </c>
       <c r="I32" s="3">
-        <v>30.641095890410959</v>
+        <v>27.463013698630139</v>
       </c>
       <c r="J32" s="22">
         <v>1</v>
@@ -2578,98 +2617,98 @@
         <v>20</v>
       </c>
       <c r="L32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M32">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N32">
-        <v>42</v>
-      </c>
-      <c r="O32" s="1">
-        <v>52.76</v>
+        <v>53</v>
+      </c>
+      <c r="O32">
+        <v>50.68</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B33">
         <v>2023</v>
       </c>
       <c r="C33" s="2">
-        <v>44983</v>
+        <v>45039</v>
       </c>
       <c r="D33" t="s">
         <v>14</v>
       </c>
-      <c r="E33" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="F33" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="G33" s="19" t="s">
-        <v>30</v>
+      <c r="E33" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="G33" s="7" t="s">
+        <v>28</v>
       </c>
       <c r="H33" s="3">
-        <v>23.857534246575341</v>
+        <v>29.12876712328767</v>
       </c>
       <c r="I33" s="3">
-        <v>25.271232876712329</v>
+        <v>32.742465753424661</v>
       </c>
       <c r="J33" s="22">
         <v>2</v>
       </c>
       <c r="K33">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L33">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M33">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N33">
-        <v>32</v>
-      </c>
-      <c r="O33" s="1">
-        <v>52.76</v>
+        <v>44</v>
+      </c>
+      <c r="O33">
+        <v>50.68</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B34">
         <v>2023</v>
       </c>
       <c r="C34" s="2">
-        <v>44983</v>
+        <v>45039</v>
       </c>
       <c r="D34" t="s">
         <v>14</v>
       </c>
-      <c r="E34" s="19" t="s">
+      <c r="E34" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="F34" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="F34" s="19" t="s">
-        <v>84</v>
-      </c>
-      <c r="G34" s="19" t="s">
+      <c r="G34" s="7" t="s">
         <v>23</v>
       </c>
       <c r="H34" s="3">
-        <v>23.323287671232876</v>
+        <v>25.161643835616438</v>
       </c>
       <c r="I34" s="3">
-        <v>22.997260273972604</v>
+        <v>23.473972602739725</v>
       </c>
       <c r="J34" s="22">
         <v>3</v>
       </c>
       <c r="K34">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L34">
         <v>6</v>
@@ -2678,227 +2717,227 @@
         <v>3</v>
       </c>
       <c r="N34">
+        <v>41</v>
+      </c>
+      <c r="O34">
+        <v>50.68</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A35" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B35" s="1">
+        <v>2023</v>
+      </c>
+      <c r="C35" s="16">
+        <v>45002</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E35" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="F35" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="G35" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="H35" s="3">
+        <v>24.186301369863013</v>
+      </c>
+      <c r="I35" s="3">
+        <v>23.906849315068492</v>
+      </c>
+      <c r="J35" s="11">
+        <v>1</v>
+      </c>
+      <c r="K35">
+        <v>0</v>
+      </c>
+      <c r="L35">
+        <v>10</v>
+      </c>
+      <c r="M35">
+        <v>4</v>
+      </c>
+      <c r="N35">
+        <v>35</v>
+      </c>
+      <c r="O35" s="6">
+        <v>50.966999999999999</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A36" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B36" s="1">
+        <v>2023</v>
+      </c>
+      <c r="C36" s="16">
+        <v>45002</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E36" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="F36" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="G36" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="H36" s="3">
+        <v>26.824657534246576</v>
+      </c>
+      <c r="I36" s="3">
+        <v>30.69041095890411</v>
+      </c>
+      <c r="J36" s="11">
+        <v>2</v>
+      </c>
+      <c r="K36">
+        <v>0</v>
+      </c>
+      <c r="L36">
+        <v>8</v>
+      </c>
+      <c r="M36">
+        <v>3</v>
+      </c>
+      <c r="N36">
+        <v>34</v>
+      </c>
+      <c r="O36" s="6">
+        <v>50.966999999999999</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A37" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B37" s="1">
+        <v>2023</v>
+      </c>
+      <c r="C37" s="16">
+        <v>45002</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E37" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="F37" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="G37" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="O34" s="1">
-        <v>52.76</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A35" t="s">
-        <v>21</v>
-      </c>
-      <c r="B35">
-        <v>2022</v>
-      </c>
-      <c r="C35" s="2">
-        <v>44850</v>
-      </c>
-      <c r="D35" t="s">
-        <v>18</v>
-      </c>
-      <c r="E35" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="F35" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="G35" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="H35" s="3">
-        <v>22.123287671232877</v>
-      </c>
-      <c r="I35" s="3">
-        <v>26.947945205479453</v>
-      </c>
-      <c r="J35" s="22">
-        <v>1</v>
-      </c>
-      <c r="K35">
-        <v>20</v>
-      </c>
-      <c r="L35">
+      <c r="H37" s="3">
+        <v>25.375342465753423</v>
+      </c>
+      <c r="I37" s="3">
+        <v>22.205479452054796</v>
+      </c>
+      <c r="J37" s="11">
         <v>3</v>
       </c>
-      <c r="M35">
-        <v>2</v>
-      </c>
-      <c r="N35">
-        <v>32</v>
-      </c>
-      <c r="O35" s="6">
-        <v>53.28</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A36" t="s">
-        <v>21</v>
-      </c>
-      <c r="B36">
-        <v>2022</v>
-      </c>
-      <c r="C36" s="2">
-        <v>44850</v>
-      </c>
-      <c r="D36" t="s">
-        <v>18</v>
-      </c>
-      <c r="E36" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="F36" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="G36" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="H36" s="3">
-        <v>23.772602739726029</v>
-      </c>
-      <c r="I36" s="3">
-        <v>23.493150684931507</v>
-      </c>
-      <c r="J36" s="22">
-        <v>2</v>
-      </c>
-      <c r="K36">
-        <v>0</v>
-      </c>
-      <c r="L36">
-        <v>9</v>
-      </c>
-      <c r="M36">
-        <v>2</v>
-      </c>
-      <c r="N36">
-        <v>31</v>
-      </c>
-      <c r="O36" s="6">
-        <v>53.28</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A37" t="s">
-        <v>21</v>
-      </c>
-      <c r="B37">
-        <v>2022</v>
-      </c>
-      <c r="C37" s="2">
-        <v>44850</v>
-      </c>
-      <c r="D37" t="s">
-        <v>18</v>
-      </c>
-      <c r="E37" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="F37" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="G37" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="H37" s="3">
-        <v>26.410958904109588</v>
-      </c>
-      <c r="I37" s="3">
-        <v>30.276712328767122</v>
-      </c>
-      <c r="J37" s="22">
+      <c r="K37">
+        <v>0</v>
+      </c>
+      <c r="L37">
+        <v>8</v>
+      </c>
+      <c r="M37">
         <v>3</v>
       </c>
-      <c r="K37">
-        <v>0</v>
-      </c>
-      <c r="L37">
-        <v>7</v>
-      </c>
-      <c r="M37">
-        <v>2</v>
-      </c>
       <c r="N37">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O37" s="6">
-        <v>53.28</v>
+        <v>50.966999999999999</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B38">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="C38" s="2">
-        <v>44751</v>
+        <v>44983</v>
       </c>
       <c r="D38" t="s">
         <v>14</v>
       </c>
       <c r="E38" s="19" t="s">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="F38" s="19" t="s">
-        <v>67</v>
-      </c>
-      <c r="G38" s="20" t="s">
-        <v>69</v>
+        <v>61</v>
+      </c>
+      <c r="G38" s="19" t="s">
+        <v>20</v>
       </c>
       <c r="H38" s="3">
-        <v>31.224657534246575</v>
+        <v>26.775342465753425</v>
       </c>
       <c r="I38" s="3">
-        <v>27.561643835616437</v>
+        <v>30.641095890410959</v>
       </c>
       <c r="J38" s="22">
         <v>1</v>
       </c>
       <c r="K38">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L38">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="M38">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="N38">
-        <v>48</v>
-      </c>
-      <c r="O38">
-        <v>48.365000000000002</v>
+        <v>42</v>
+      </c>
+      <c r="O38" s="1">
+        <v>52.76</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B39">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="C39" s="2">
-        <v>44751</v>
+        <v>44983</v>
       </c>
       <c r="D39" t="s">
         <v>14</v>
       </c>
       <c r="E39" s="19" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="F39" s="19" t="s">
-        <v>87</v>
-      </c>
-      <c r="G39" s="20" t="s">
-        <v>23</v>
+        <v>52</v>
+      </c>
+      <c r="G39" s="19" t="s">
+        <v>30</v>
       </c>
       <c r="H39" s="3">
-        <v>23.246575342465754</v>
+        <v>23.857534246575341</v>
       </c>
       <c r="I39" s="3">
-        <v>22.983561643835618</v>
+        <v>25.271232876712329</v>
       </c>
       <c r="J39" s="22">
         <v>2</v>
@@ -2910,42 +2949,42 @@
         <v>10</v>
       </c>
       <c r="M39">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N39">
-        <v>35</v>
-      </c>
-      <c r="O39">
-        <v>48.365000000000002</v>
+        <v>32</v>
+      </c>
+      <c r="O39" s="1">
+        <v>52.76</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B40">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="C40" s="2">
-        <v>44751</v>
+        <v>44983</v>
       </c>
       <c r="D40" t="s">
         <v>14</v>
       </c>
       <c r="E40" s="19" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="F40" s="19" t="s">
-        <v>89</v>
-      </c>
-      <c r="G40" s="20" t="s">
-        <v>26</v>
+        <v>84</v>
+      </c>
+      <c r="G40" s="19" t="s">
+        <v>23</v>
       </c>
       <c r="H40" s="3">
-        <v>24.279452054794522</v>
+        <v>23.323287671232876</v>
       </c>
       <c r="I40" s="3">
-        <v>19.86849315068493</v>
+        <v>22.997260273972604</v>
       </c>
       <c r="J40" s="22">
         <v>3</v>
@@ -2954,45 +2993,45 @@
         <v>0</v>
       </c>
       <c r="L40">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M40">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N40">
-        <v>29</v>
-      </c>
-      <c r="O40">
-        <v>48.365000000000002</v>
+        <v>26</v>
+      </c>
+      <c r="O40" s="1">
+        <v>52.76</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B41">
         <v>2022</v>
       </c>
       <c r="C41" s="2">
-        <v>44695</v>
+        <v>44850</v>
       </c>
       <c r="D41" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="F41" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="G41" s="21" t="s">
-        <v>23</v>
+        <v>79</v>
+      </c>
+      <c r="F41" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="G41" s="11" t="s">
+        <v>16</v>
       </c>
       <c r="H41" s="3">
-        <v>24.227397260273971</v>
+        <v>22.123287671232877</v>
       </c>
       <c r="I41" s="3">
-        <v>22.906849315068492</v>
+        <v>26.947945205479453</v>
       </c>
       <c r="J41" s="22">
         <v>1</v>
@@ -3001,139 +3040,139 @@
         <v>20</v>
       </c>
       <c r="L41">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="M41">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N41">
-        <v>54</v>
-      </c>
-      <c r="O41">
-        <v>51.527000000000001</v>
+        <v>32</v>
+      </c>
+      <c r="O41" s="6">
+        <v>53.28</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B42">
         <v>2022</v>
       </c>
       <c r="C42" s="2">
-        <v>44695</v>
+        <v>44850</v>
       </c>
       <c r="D42" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="G42" s="21" t="s">
-        <v>42</v>
+        <v>66</v>
+      </c>
+      <c r="G42" s="11" t="s">
+        <v>30</v>
       </c>
       <c r="H42" s="3">
-        <v>26.227397260273971</v>
+        <v>23.772602739726029</v>
       </c>
       <c r="I42" s="3">
-        <v>23.509589041095889</v>
+        <v>23.493150684931507</v>
       </c>
       <c r="J42" s="22">
         <v>2</v>
       </c>
       <c r="K42">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="L42">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M42">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N42">
-        <v>45</v>
-      </c>
-      <c r="O42">
-        <v>51.527000000000001</v>
+        <v>31</v>
+      </c>
+      <c r="O42" s="6">
+        <v>53.28</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B43">
         <v>2022</v>
       </c>
       <c r="C43" s="2">
-        <v>44695</v>
+        <v>44850</v>
       </c>
       <c r="D43" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E43" s="11" t="s">
-        <v>91</v>
+        <v>55</v>
       </c>
       <c r="F43" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="G43" s="21" t="s">
-        <v>93</v>
+        <v>61</v>
+      </c>
+      <c r="G43" s="11" t="s">
+        <v>20</v>
       </c>
       <c r="H43" s="3">
-        <v>23.389041095890413</v>
+        <v>26.410958904109588</v>
       </c>
       <c r="I43" s="3">
-        <v>28.052054794520547</v>
+        <v>30.276712328767122</v>
       </c>
       <c r="J43" s="22">
         <v>3</v>
       </c>
       <c r="K43">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="L43">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M43">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N43">
-        <v>29</v>
-      </c>
-      <c r="O43">
-        <v>51.527000000000001</v>
+        <v>23</v>
+      </c>
+      <c r="O43" s="6">
+        <v>53.28</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B44">
         <v>2022</v>
       </c>
       <c r="C44" s="2">
-        <v>44674</v>
+        <v>44751</v>
       </c>
       <c r="D44" t="s">
         <v>14</v>
       </c>
       <c r="E44" s="19" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="F44" s="19" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G44" s="20" t="s">
-        <v>30</v>
+        <v>69</v>
       </c>
       <c r="H44" s="3">
-        <v>24.43013698630137</v>
+        <v>31.224657534246575</v>
       </c>
       <c r="I44" s="3">
-        <v>23.016438356164382</v>
+        <v>27.561643835616437</v>
       </c>
       <c r="J44" s="22">
         <v>1</v>
@@ -3142,45 +3181,45 @@
         <v>0</v>
       </c>
       <c r="L44">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="M44">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N44">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="O44">
-        <v>38.933</v>
+        <v>48.365000000000002</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B45">
         <v>2022</v>
       </c>
       <c r="C45" s="2">
-        <v>44674</v>
+        <v>44751</v>
       </c>
       <c r="D45" t="s">
         <v>14</v>
       </c>
       <c r="E45" s="19" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="F45" s="19" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="G45" s="20" t="s">
         <v>23</v>
       </c>
       <c r="H45" s="3">
-        <v>24.169863013698631</v>
+        <v>23.246575342465754</v>
       </c>
       <c r="I45" s="3">
-        <v>21.339726027397262</v>
+        <v>22.983561643835618</v>
       </c>
       <c r="J45" s="22">
         <v>2</v>
@@ -3189,45 +3228,45 @@
         <v>0</v>
       </c>
       <c r="L45">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M45">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N45">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="O45">
-        <v>38.933</v>
+        <v>48.365000000000002</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B46">
         <v>2022</v>
       </c>
       <c r="C46" s="2">
-        <v>44674</v>
+        <v>44751</v>
       </c>
       <c r="D46" t="s">
         <v>14</v>
       </c>
       <c r="E46" s="19" t="s">
-        <v>55</v>
+        <v>88</v>
       </c>
       <c r="F46" s="19" t="s">
-        <v>61</v>
+        <v>89</v>
       </c>
       <c r="G46" s="20" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="H46" s="3">
-        <v>25.934246575342467</v>
+        <v>24.279452054794522</v>
       </c>
       <c r="I46" s="3">
-        <v>29.8</v>
+        <v>19.86849315068493</v>
       </c>
       <c r="J46" s="22">
         <v>3</v>
@@ -3236,468 +3275,468 @@
         <v>0</v>
       </c>
       <c r="L46">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M46">
         <v>1</v>
       </c>
       <c r="N46">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="O46">
-        <v>38.933</v>
+        <v>48.365000000000002</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="B47">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="C47" s="2">
-        <v>44493</v>
+        <v>44695</v>
       </c>
       <c r="D47" t="s">
-        <v>18</v>
-      </c>
-      <c r="E47" s="5" t="s">
-        <v>94</v>
+        <v>14</v>
+      </c>
+      <c r="E47" s="11" t="s">
+        <v>81</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="G47" s="5" t="s">
-        <v>15</v>
+        <v>53</v>
+      </c>
+      <c r="G47" s="21" t="s">
+        <v>23</v>
       </c>
       <c r="H47" s="3">
-        <v>30.416438356164385</v>
+        <v>24.227397260273971</v>
       </c>
       <c r="I47" s="3">
-        <v>39.049315068493151</v>
-      </c>
-      <c r="J47" s="6">
+        <v>22.906849315068492</v>
+      </c>
+      <c r="J47" s="22">
         <v>1</v>
       </c>
       <c r="K47">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L47">
         <v>9</v>
       </c>
       <c r="M47">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N47">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="O47">
-        <v>52.838000000000001</v>
+        <v>51.527000000000001</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
+        <v>24</v>
+      </c>
+      <c r="B48">
+        <v>2022</v>
+      </c>
+      <c r="C48" s="2">
+        <v>44695</v>
+      </c>
+      <c r="D48" t="s">
+        <v>14</v>
+      </c>
+      <c r="E48" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="F48" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="G48" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="H48" s="3">
+        <v>26.227397260273971</v>
+      </c>
+      <c r="I48" s="3">
+        <v>23.509589041095889</v>
+      </c>
+      <c r="J48" s="22">
+        <v>2</v>
+      </c>
+      <c r="K48">
+        <v>20</v>
+      </c>
+      <c r="L48">
+        <v>6</v>
+      </c>
+      <c r="M48">
+        <v>3</v>
+      </c>
+      <c r="N48">
+        <v>45</v>
+      </c>
+      <c r="O48">
+        <v>51.527000000000001</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B49">
+        <v>2022</v>
+      </c>
+      <c r="C49" s="2">
+        <v>44695</v>
+      </c>
+      <c r="D49" t="s">
+        <v>14</v>
+      </c>
+      <c r="E49" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="F49" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="G49" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="H49" s="3">
+        <v>23.389041095890413</v>
+      </c>
+      <c r="I49" s="3">
+        <v>28.052054794520547</v>
+      </c>
+      <c r="J49" s="22">
+        <v>3</v>
+      </c>
+      <c r="K49">
+        <v>20</v>
+      </c>
+      <c r="L49">
+        <v>5</v>
+      </c>
+      <c r="M49">
+        <v>0</v>
+      </c>
+      <c r="N49">
+        <v>29</v>
+      </c>
+      <c r="O49">
+        <v>51.527000000000001</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A50" t="s">
+        <v>29</v>
+      </c>
+      <c r="B50">
+        <v>2022</v>
+      </c>
+      <c r="C50" s="2">
+        <v>44674</v>
+      </c>
+      <c r="D50" t="s">
+        <v>14</v>
+      </c>
+      <c r="E50" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="F50" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="G50" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="H50" s="3">
+        <v>24.43013698630137</v>
+      </c>
+      <c r="I50" s="3">
+        <v>23.016438356164382</v>
+      </c>
+      <c r="J50" s="22">
+        <v>1</v>
+      </c>
+      <c r="K50">
+        <v>0</v>
+      </c>
+      <c r="L50">
+        <v>8</v>
+      </c>
+      <c r="M50">
+        <v>5</v>
+      </c>
+      <c r="N50">
+        <v>33</v>
+      </c>
+      <c r="O50">
+        <v>38.933</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A51" t="s">
+        <v>29</v>
+      </c>
+      <c r="B51">
+        <v>2022</v>
+      </c>
+      <c r="C51" s="2">
+        <v>44674</v>
+      </c>
+      <c r="D51" t="s">
+        <v>14</v>
+      </c>
+      <c r="E51" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="F51" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="G51" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="H51" s="3">
+        <v>24.169863013698631</v>
+      </c>
+      <c r="I51" s="3">
+        <v>21.339726027397262</v>
+      </c>
+      <c r="J51" s="22">
+        <v>2</v>
+      </c>
+      <c r="K51">
+        <v>0</v>
+      </c>
+      <c r="L51">
+        <v>7</v>
+      </c>
+      <c r="M51">
+        <v>1</v>
+      </c>
+      <c r="N51">
+        <v>23</v>
+      </c>
+      <c r="O51">
+        <v>38.933</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A52" t="s">
+        <v>29</v>
+      </c>
+      <c r="B52">
+        <v>2022</v>
+      </c>
+      <c r="C52" s="2">
+        <v>44674</v>
+      </c>
+      <c r="D52" t="s">
+        <v>14</v>
+      </c>
+      <c r="E52" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="F52" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="G52" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="H52" s="3">
+        <v>25.934246575342467</v>
+      </c>
+      <c r="I52" s="3">
+        <v>29.8</v>
+      </c>
+      <c r="J52" s="22">
+        <v>3</v>
+      </c>
+      <c r="K52">
+        <v>0</v>
+      </c>
+      <c r="L52">
+        <v>6</v>
+      </c>
+      <c r="M52">
+        <v>1</v>
+      </c>
+      <c r="N52">
+        <v>18</v>
+      </c>
+      <c r="O52">
+        <v>38.933</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A53" t="s">
         <v>35</v>
       </c>
-      <c r="B48">
+      <c r="B53">
         <v>2021</v>
       </c>
-      <c r="C48" s="2">
+      <c r="C53" s="2">
         <v>44493</v>
       </c>
-      <c r="D48" t="s">
+      <c r="D53" t="s">
         <v>18</v>
       </c>
-      <c r="E48" s="5" t="s">
+      <c r="E53" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="F53" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="G53" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H53" s="3">
+        <v>30.416438356164385</v>
+      </c>
+      <c r="I53" s="3">
+        <v>39.049315068493151</v>
+      </c>
+      <c r="J53" s="6">
+        <v>1</v>
+      </c>
+      <c r="K53">
+        <v>0</v>
+      </c>
+      <c r="L53">
+        <v>9</v>
+      </c>
+      <c r="M53">
+        <v>4</v>
+      </c>
+      <c r="N53">
+        <v>35</v>
+      </c>
+      <c r="O53">
+        <v>52.838000000000001</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A54" t="s">
+        <v>35</v>
+      </c>
+      <c r="B54">
+        <v>2021</v>
+      </c>
+      <c r="C54" s="2">
+        <v>44493</v>
+      </c>
+      <c r="D54" t="s">
+        <v>18</v>
+      </c>
+      <c r="E54" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="F48" s="5" t="s">
+      <c r="F54" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="G48" s="5" t="s">
+      <c r="G54" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="H48" s="3">
+      <c r="H54" s="3">
         <v>22.794520547945204</v>
       </c>
-      <c r="I48" s="3">
+      <c r="I54" s="3">
         <v>21.758904109589039</v>
       </c>
-      <c r="J48" s="6">
+      <c r="J54" s="6">
         <v>2</v>
       </c>
-      <c r="K48">
-        <v>0</v>
-      </c>
-      <c r="L48">
+      <c r="K54">
+        <v>0</v>
+      </c>
+      <c r="L54">
         <v>9</v>
       </c>
-      <c r="M48">
+      <c r="M54">
         <v>2</v>
       </c>
-      <c r="N48">
+      <c r="N54">
         <v>30</v>
       </c>
-      <c r="O48">
+      <c r="O54">
         <v>52.838000000000001</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A49" s="7" t="s">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A55" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B49" s="7">
+      <c r="B55" s="7">
         <v>2021</v>
       </c>
-      <c r="C49" s="8">
+      <c r="C55" s="8">
         <v>44493</v>
       </c>
-      <c r="D49" s="7" t="s">
+      <c r="D55" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E49" s="5" t="s">
+      <c r="E55" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F49" s="5" t="s">
+      <c r="F55" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="G49" s="5" t="s">
+      <c r="G55" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="H49" s="3">
+      <c r="H55" s="3">
         <v>27.635616438356163</v>
       </c>
-      <c r="I49" s="3">
+      <c r="I55" s="3">
         <v>31.24931506849315</v>
       </c>
-      <c r="J49" s="6">
+      <c r="J55" s="6">
         <v>3</v>
       </c>
-      <c r="K49">
-        <v>0</v>
-      </c>
-      <c r="L49">
+      <c r="K55">
+        <v>0</v>
+      </c>
+      <c r="L55">
         <v>10</v>
       </c>
-      <c r="M49">
+      <c r="M55">
         <v>1</v>
       </c>
-      <c r="N49">
+      <c r="N55">
         <v>24</v>
       </c>
-      <c r="O49">
+      <c r="O55">
         <v>52.838000000000001</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A50" s="7" t="s">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A56" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B50" s="7">
+      <c r="B56" s="7">
         <v>2021</v>
       </c>
-      <c r="C50" s="8">
+      <c r="C56" s="8">
         <v>44450</v>
       </c>
-      <c r="D50" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E50" s="1" t="s">
+      <c r="D56" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E56" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="F50" s="1" t="s">
+      <c r="F56" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="G50" s="1" t="s">
+      <c r="G56" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="H50" s="3">
+      <c r="H56" s="3">
         <v>24.69041095890411</v>
       </c>
-      <c r="I50" s="3">
+      <c r="I56" s="3">
         <v>23.252054794520546</v>
-      </c>
-      <c r="J50" s="6">
-        <v>1</v>
-      </c>
-      <c r="K50">
-        <v>0</v>
-      </c>
-      <c r="L50">
-        <v>11</v>
-      </c>
-      <c r="M50">
-        <v>10</v>
-      </c>
-      <c r="N50">
-        <v>53</v>
-      </c>
-      <c r="O50">
-        <v>48.615000000000002</v>
-      </c>
-    </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A51" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="B51" s="7">
-        <v>2021</v>
-      </c>
-      <c r="C51" s="8">
-        <v>44450</v>
-      </c>
-      <c r="D51" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="F51" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="G51" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="H51" s="3">
-        <v>23.709589041095889</v>
-      </c>
-      <c r="I51" s="3">
-        <v>27.358904109589041</v>
-      </c>
-      <c r="J51" s="6">
-        <v>2</v>
-      </c>
-      <c r="K51">
-        <v>0</v>
-      </c>
-      <c r="L51">
-        <v>9</v>
-      </c>
-      <c r="M51">
-        <v>0</v>
-      </c>
-      <c r="N51">
-        <v>22</v>
-      </c>
-      <c r="O51">
-        <v>48.615000000000002</v>
-      </c>
-    </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A52" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="B52" s="9">
-        <v>2021</v>
-      </c>
-      <c r="C52" s="10">
-        <v>44450</v>
-      </c>
-      <c r="D52" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="F52" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="G52" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="H52" s="3">
-        <v>22.695890410958903</v>
-      </c>
-      <c r="I52" s="3">
-        <v>20.873972602739727</v>
-      </c>
-      <c r="J52" s="6">
-        <v>3</v>
-      </c>
-      <c r="K52">
-        <v>0</v>
-      </c>
-      <c r="L52">
-        <v>10</v>
-      </c>
-      <c r="M52">
-        <v>0</v>
-      </c>
-      <c r="N52">
-        <v>21</v>
-      </c>
-      <c r="O52">
-        <v>48.615000000000002</v>
-      </c>
-    </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A53" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="B53" s="11">
-        <v>2021</v>
-      </c>
-      <c r="C53" s="12">
-        <v>44415</v>
-      </c>
-      <c r="D53" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="E53" t="s">
-        <v>50</v>
-      </c>
-      <c r="F53" t="s">
-        <v>105</v>
-      </c>
-      <c r="G53" t="s">
-        <v>28</v>
-      </c>
-      <c r="H53" s="3">
-        <v>27.421917808219177</v>
-      </c>
-      <c r="I53" s="3">
-        <v>29.304109589041097</v>
-      </c>
-      <c r="J53" s="5">
-        <v>1</v>
-      </c>
-      <c r="K53" s="11">
-        <v>20</v>
-      </c>
-      <c r="L53">
-        <v>12</v>
-      </c>
-      <c r="M53">
-        <v>10</v>
-      </c>
-      <c r="N53" s="11">
-        <v>78</v>
-      </c>
-      <c r="O53" s="6">
-        <v>54.947000000000003</v>
-      </c>
-    </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A54" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="B54" s="11">
-        <v>2021</v>
-      </c>
-      <c r="C54" s="12">
-        <v>44415</v>
-      </c>
-      <c r="D54" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="E54" t="s">
-        <v>55</v>
-      </c>
-      <c r="F54" t="s">
-        <v>61</v>
-      </c>
-      <c r="G54" t="s">
-        <v>20</v>
-      </c>
-      <c r="H54" s="3">
-        <v>25.219178082191782</v>
-      </c>
-      <c r="I54" s="3">
-        <v>29.084931506849315</v>
-      </c>
-      <c r="J54" s="5">
-        <v>2</v>
-      </c>
-      <c r="K54" s="11">
-        <v>20</v>
-      </c>
-      <c r="L54">
-        <v>7</v>
-      </c>
-      <c r="M54">
-        <v>0</v>
-      </c>
-      <c r="N54" s="11">
-        <v>35</v>
-      </c>
-      <c r="O54" s="6">
-        <v>54.947000000000003</v>
-      </c>
-    </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A55" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="B55" s="11">
-        <v>2021</v>
-      </c>
-      <c r="C55" s="12">
-        <v>44415</v>
-      </c>
-      <c r="D55" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="E55" t="s">
-        <v>106</v>
-      </c>
-      <c r="F55" t="s">
-        <v>107</v>
-      </c>
-      <c r="G55" t="s">
-        <v>108</v>
-      </c>
-      <c r="H55" s="3">
-        <v>27.312328767123287</v>
-      </c>
-      <c r="I55" s="3">
-        <v>22.041095890410958</v>
-      </c>
-      <c r="J55" s="5">
-        <v>3</v>
-      </c>
-      <c r="K55" s="11">
-        <v>20</v>
-      </c>
-      <c r="L55">
-        <v>3</v>
-      </c>
-      <c r="M55">
-        <v>0</v>
-      </c>
-      <c r="N55" s="11">
-        <v>26</v>
-      </c>
-      <c r="O55" s="6">
-        <v>54.947000000000003</v>
-      </c>
-    </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A56" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="B56" s="13">
-        <v>2021</v>
-      </c>
-      <c r="C56" s="2">
-        <v>44387</v>
-      </c>
-      <c r="D56" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E56" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="F56" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="G56" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="H56" s="3">
-        <v>27.241095890410961</v>
-      </c>
-      <c r="I56" s="3">
-        <v>24.772602739726029</v>
       </c>
       <c r="J56" s="6">
         <v>1</v>
@@ -3706,45 +3745,45 @@
         <v>0</v>
       </c>
       <c r="L56">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M56">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="N56">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="O56">
-        <v>48.585000000000001</v>
+        <v>48.615000000000002</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A57" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="B57" s="13">
+      <c r="A57" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B57" s="7">
         <v>2021</v>
       </c>
-      <c r="C57" s="2">
-        <v>44387</v>
+      <c r="C57" s="8">
+        <v>44450</v>
       </c>
       <c r="D57" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="E57" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="F57" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="G57" s="5" t="s">
-        <v>38</v>
+      <c r="E57" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>102</v>
       </c>
       <c r="H57" s="3">
-        <v>18.323287671232876</v>
+        <v>23.709589041095889</v>
       </c>
       <c r="I57" s="3">
-        <v>17.663013698630138</v>
+        <v>27.358904109589041</v>
       </c>
       <c r="J57" s="6">
         <v>2</v>
@@ -3753,45 +3792,45 @@
         <v>0</v>
       </c>
       <c r="L57">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="M57">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N57">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="O57">
-        <v>48.585000000000001</v>
+        <v>48.615000000000002</v>
       </c>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A58" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="B58" s="13">
+      <c r="A58" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B58" s="9">
         <v>2021</v>
       </c>
-      <c r="C58" s="2">
-        <v>44387</v>
-      </c>
-      <c r="D58" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E58" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="F58" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="G58" s="5" t="s">
-        <v>114</v>
+      <c r="C58" s="10">
+        <v>44450</v>
+      </c>
+      <c r="D58" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="H58" s="3">
-        <v>24.410958904109588</v>
+        <v>22.695890410958903</v>
       </c>
       <c r="I58" s="3">
-        <v>24.142465753424659</v>
+        <v>20.873972602739727</v>
       </c>
       <c r="J58" s="6">
         <v>3</v>
@@ -3800,186 +3839,186 @@
         <v>0</v>
       </c>
       <c r="L58">
+        <v>10</v>
+      </c>
+      <c r="M58">
+        <v>0</v>
+      </c>
+      <c r="N58">
+        <v>21</v>
+      </c>
+      <c r="O58">
+        <v>48.615000000000002</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A59" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B59" s="11">
+        <v>2021</v>
+      </c>
+      <c r="C59" s="12">
+        <v>44415</v>
+      </c>
+      <c r="D59" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="E59" t="s">
+        <v>50</v>
+      </c>
+      <c r="F59" t="s">
+        <v>105</v>
+      </c>
+      <c r="G59" t="s">
+        <v>28</v>
+      </c>
+      <c r="H59" s="3">
+        <v>27.421917808219177</v>
+      </c>
+      <c r="I59" s="3">
+        <v>29.304109589041097</v>
+      </c>
+      <c r="J59" s="5">
+        <v>1</v>
+      </c>
+      <c r="K59" s="11">
+        <v>20</v>
+      </c>
+      <c r="L59">
         <v>12</v>
       </c>
-      <c r="M58">
-        <v>1</v>
-      </c>
-      <c r="N58">
-        <v>32</v>
-      </c>
-      <c r="O58">
-        <v>48.585000000000001</v>
-      </c>
-    </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A59" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B59" s="7">
-        <v>2020</v>
-      </c>
-      <c r="C59" s="8">
-        <v>43891</v>
-      </c>
-      <c r="D59" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E59" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="F59" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="G59" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H59" s="3">
-        <v>37.4</v>
-      </c>
-      <c r="I59" s="3">
-        <v>28.767123287671232</v>
-      </c>
-      <c r="J59" s="6">
-        <v>1</v>
-      </c>
-      <c r="K59">
-        <v>0</v>
-      </c>
-      <c r="L59">
-        <v>11</v>
-      </c>
       <c r="M59">
+        <v>10</v>
+      </c>
+      <c r="N59" s="11">
+        <v>78</v>
+      </c>
+      <c r="O59" s="6">
+        <v>54.947000000000003</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A60" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B60" s="11">
+        <v>2021</v>
+      </c>
+      <c r="C60" s="12">
+        <v>44415</v>
+      </c>
+      <c r="D60" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="E60" t="s">
+        <v>55</v>
+      </c>
+      <c r="F60" t="s">
+        <v>61</v>
+      </c>
+      <c r="G60" t="s">
+        <v>20</v>
+      </c>
+      <c r="H60" s="3">
+        <v>25.219178082191782</v>
+      </c>
+      <c r="I60" s="3">
+        <v>29.084931506849315</v>
+      </c>
+      <c r="J60" s="5">
+        <v>2</v>
+      </c>
+      <c r="K60" s="11">
+        <v>20</v>
+      </c>
+      <c r="L60">
+        <v>7</v>
+      </c>
+      <c r="M60">
+        <v>0</v>
+      </c>
+      <c r="N60" s="11">
+        <v>35</v>
+      </c>
+      <c r="O60" s="6">
+        <v>54.947000000000003</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A61" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B61" s="11">
+        <v>2021</v>
+      </c>
+      <c r="C61" s="12">
+        <v>44415</v>
+      </c>
+      <c r="D61" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="E61" t="s">
+        <v>106</v>
+      </c>
+      <c r="F61" t="s">
+        <v>107</v>
+      </c>
+      <c r="G61" t="s">
+        <v>108</v>
+      </c>
+      <c r="H61" s="3">
+        <v>27.312328767123287</v>
+      </c>
+      <c r="I61" s="3">
+        <v>22.041095890410958</v>
+      </c>
+      <c r="J61" s="5">
         <v>3</v>
       </c>
-      <c r="N59">
-        <v>36</v>
-      </c>
-      <c r="O59" s="5">
-        <v>50.908000000000001</v>
-      </c>
-    </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A60" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B60" s="7">
-        <v>2020</v>
-      </c>
-      <c r="C60" s="8">
-        <v>43891</v>
-      </c>
-      <c r="D60" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E60" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="F60" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="G60" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H60" s="3">
-        <v>21.145205479452056</v>
-      </c>
-      <c r="I60" s="3">
-        <v>20.109589041095891</v>
-      </c>
-      <c r="J60" s="6">
-        <v>2</v>
-      </c>
-      <c r="K60">
-        <v>0</v>
-      </c>
-      <c r="L60">
-        <v>6</v>
-      </c>
-      <c r="M60">
+      <c r="K61" s="11">
+        <v>20</v>
+      </c>
+      <c r="L61">
         <v>3</v>
       </c>
-      <c r="N60">
-        <v>24</v>
-      </c>
-      <c r="O60" s="5">
-        <v>50.908000000000001</v>
-      </c>
-    </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A61" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B61" s="7">
-        <v>2020</v>
-      </c>
-      <c r="C61" s="8">
-        <v>43891</v>
-      </c>
-      <c r="D61" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="F61" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="G61" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H61" s="3">
-        <v>20.621917808219177</v>
-      </c>
-      <c r="I61" s="3">
-        <v>22.019178082191782</v>
-      </c>
-      <c r="J61" s="6">
-        <v>3</v>
-      </c>
-      <c r="K61">
-        <v>0</v>
-      </c>
-      <c r="L61">
-        <v>6</v>
-      </c>
       <c r="M61">
-        <v>2</v>
-      </c>
-      <c r="N61">
-        <v>20</v>
-      </c>
-      <c r="O61" s="5">
-        <v>50.908000000000001</v>
+        <v>0</v>
+      </c>
+      <c r="N61" s="11">
+        <v>26</v>
+      </c>
+      <c r="O61" s="6">
+        <v>54.947000000000003</v>
       </c>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A62" s="13" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="B62" s="13">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C62" s="2">
-        <v>43856</v>
-      </c>
-      <c r="D62" s="13" t="s">
+        <v>44387</v>
+      </c>
+      <c r="D62" s="7" t="s">
         <v>14</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>62</v>
+        <v>106</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="G62" s="5" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="H62" s="3">
-        <v>29.504109589041096</v>
+        <v>27.241095890410961</v>
       </c>
       <c r="I62" s="3">
-        <v>27.772602739726029</v>
+        <v>24.772602739726029</v>
       </c>
       <c r="J62" s="6">
         <v>1</v>
@@ -3988,43 +4027,45 @@
         <v>0</v>
       </c>
       <c r="L62">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="M62">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N62">
-        <v>30</v>
-      </c>
-      <c r="O62" s="24"/>
+        <v>50</v>
+      </c>
+      <c r="O62">
+        <v>48.585000000000001</v>
+      </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A63" s="13" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="B63" s="13">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C63" s="2">
-        <v>43856</v>
-      </c>
-      <c r="D63" s="13" t="s">
+        <v>44387</v>
+      </c>
+      <c r="D63" s="7" t="s">
         <v>14</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>80</v>
+        <v>111</v>
       </c>
       <c r="G63" s="5" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="H63" s="3">
-        <v>29.887671232876713</v>
+        <v>18.323287671232876</v>
       </c>
       <c r="I63" s="3">
-        <v>24.224657534246575</v>
+        <v>17.663013698630138</v>
       </c>
       <c r="J63" s="6">
         <v>2</v>
@@ -4033,43 +4074,45 @@
         <v>0</v>
       </c>
       <c r="L63">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M63">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N63">
-        <v>28</v>
-      </c>
-      <c r="O63" s="24"/>
+        <v>41</v>
+      </c>
+      <c r="O63">
+        <v>48.585000000000001</v>
+      </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A64" s="13" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="B64" s="13">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C64" s="2">
-        <v>43856</v>
-      </c>
-      <c r="D64" s="13" t="s">
+        <v>44387</v>
+      </c>
+      <c r="D64" s="7" t="s">
         <v>14</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>67</v>
+        <v>113</v>
       </c>
       <c r="G64" s="5" t="s">
-        <v>69</v>
+        <v>114</v>
       </c>
       <c r="H64" s="3">
-        <v>18</v>
+        <v>24.410958904109588</v>
       </c>
       <c r="I64" s="3">
-        <v>25.104109589041094</v>
+        <v>24.142465753424659</v>
       </c>
       <c r="J64" s="6">
         <v>3</v>
@@ -4078,75 +4121,77 @@
         <v>0</v>
       </c>
       <c r="L64">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="M64">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N64">
-        <v>24</v>
-      </c>
-      <c r="O64" s="24"/>
+        <v>32</v>
+      </c>
+      <c r="O64">
+        <v>48.585000000000001</v>
+      </c>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A65" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="B65" s="13">
-        <v>2019</v>
-      </c>
-      <c r="C65" s="2">
-        <v>43814</v>
-      </c>
-      <c r="D65" s="13" t="s">
-        <v>14</v>
+      <c r="A65" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B65" s="7">
+        <v>2020</v>
+      </c>
+      <c r="C65" s="8">
+        <v>43891</v>
+      </c>
+      <c r="D65" s="7" t="s">
+        <v>18</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>117</v>
+        <v>94</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="H65" s="3">
-        <v>25.246575342465754</v>
+        <v>37.4</v>
       </c>
       <c r="I65" s="3">
-        <v>28.024657534246575</v>
+        <v>28.767123287671232</v>
       </c>
       <c r="J65" s="6">
         <v>1</v>
       </c>
       <c r="K65">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="L65">
         <v>11</v>
       </c>
       <c r="M65">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N65">
-        <v>56</v>
-      </c>
-      <c r="O65" s="24">
-        <v>48.262</v>
+        <v>36</v>
+      </c>
+      <c r="O65" s="5">
+        <v>50.908000000000001</v>
       </c>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A66" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="B66" s="13">
-        <v>2019</v>
-      </c>
-      <c r="C66" s="2">
-        <v>43814</v>
-      </c>
-      <c r="D66" s="13" t="s">
-        <v>14</v>
+      <c r="A66" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B66" s="7">
+        <v>2020</v>
+      </c>
+      <c r="C66" s="8">
+        <v>43891</v>
+      </c>
+      <c r="D66" s="7" t="s">
+        <v>18</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>78</v>
@@ -4158,104 +4203,104 @@
         <v>30</v>
       </c>
       <c r="H66" s="3">
-        <v>20.934246575342467</v>
+        <v>21.145205479452056</v>
       </c>
       <c r="I66" s="3">
-        <v>19.898630136986302</v>
+        <v>20.109589041095891</v>
       </c>
       <c r="J66" s="6">
         <v>2</v>
       </c>
       <c r="K66">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="L66">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M66">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N66">
-        <v>51</v>
-      </c>
-      <c r="O66" s="24">
-        <v>48.262</v>
+        <v>24</v>
+      </c>
+      <c r="O66" s="5">
+        <v>50.908000000000001</v>
       </c>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A67" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="B67" s="13">
-        <v>2019</v>
-      </c>
-      <c r="C67" s="2">
-        <v>43814</v>
-      </c>
-      <c r="D67" s="13" t="s">
-        <v>14</v>
+      <c r="A67" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B67" s="7">
+        <v>2020</v>
+      </c>
+      <c r="C67" s="8">
+        <v>43891</v>
+      </c>
+      <c r="D67" s="7" t="s">
+        <v>18</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>118</v>
+        <v>87</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>119</v>
+        <v>81</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>69</v>
+        <v>23</v>
       </c>
       <c r="H67" s="3">
-        <v>27.361643835616437</v>
+        <v>20.621917808219177</v>
       </c>
       <c r="I67" s="3">
-        <v>33.095890410958901</v>
+        <v>22.019178082191782</v>
       </c>
       <c r="J67" s="6">
         <v>3</v>
       </c>
       <c r="K67">
+        <v>0</v>
+      </c>
+      <c r="L67">
+        <v>6</v>
+      </c>
+      <c r="M67">
+        <v>2</v>
+      </c>
+      <c r="N67">
         <v>20</v>
       </c>
-      <c r="L67">
-        <v>4</v>
-      </c>
-      <c r="M67">
-        <v>1</v>
-      </c>
-      <c r="N67">
-        <v>32</v>
-      </c>
-      <c r="O67" s="24">
-        <v>48.262</v>
+      <c r="O67" s="5">
+        <v>50.908000000000001</v>
       </c>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A68" s="13" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="B68" s="13">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="C68" s="2">
-        <v>43807</v>
+        <v>43856</v>
       </c>
       <c r="D68" s="13" t="s">
         <v>14</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="G68" s="5" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="H68" s="3">
-        <v>25.227397260273971</v>
+        <v>29.504109589041096</v>
       </c>
       <c r="I68" s="3">
-        <v>23.789041095890411</v>
+        <v>27.772602739726029</v>
       </c>
       <c r="J68" s="6">
         <v>1</v>
@@ -4264,45 +4309,43 @@
         <v>0</v>
       </c>
       <c r="L68">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M68">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N68">
-        <v>42</v>
-      </c>
-      <c r="O68" s="24">
-        <v>49.936</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="O68" s="24"/>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A69" s="13" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="B69" s="13">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="C69" s="2">
-        <v>43807</v>
+        <v>43856</v>
       </c>
       <c r="D69" s="13" t="s">
         <v>14</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="F69" s="5" t="s">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="G69" s="5" t="s">
-        <v>99</v>
+        <v>16</v>
       </c>
       <c r="H69" s="3">
-        <v>22.931506849315067</v>
+        <v>29.887671232876713</v>
       </c>
       <c r="I69" s="3">
-        <v>23.55890410958904</v>
+        <v>24.224657534246575</v>
       </c>
       <c r="J69" s="6">
         <v>2</v>
@@ -4311,45 +4354,43 @@
         <v>0</v>
       </c>
       <c r="L69">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="M69">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N69">
-        <v>32</v>
-      </c>
-      <c r="O69" s="24">
-        <v>49.936</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="O69" s="24"/>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A70" s="13" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="B70" s="13">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="C70" s="2">
-        <v>43807</v>
+        <v>43856</v>
       </c>
       <c r="D70" s="13" t="s">
         <v>14</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>88</v>
+        <v>116</v>
       </c>
       <c r="F70" s="5" t="s">
-        <v>121</v>
+        <v>67</v>
       </c>
       <c r="G70" s="5" t="s">
-        <v>122</v>
+        <v>69</v>
       </c>
       <c r="H70" s="3">
-        <v>21.687671232876713</v>
+        <v>18</v>
       </c>
       <c r="I70" s="3">
-        <v>23.147945205479452</v>
+        <v>25.104109589041094</v>
       </c>
       <c r="J70" s="6">
         <v>3</v>
@@ -4358,186 +4399,184 @@
         <v>0</v>
       </c>
       <c r="L70">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M70">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N70">
-        <v>19</v>
-      </c>
-      <c r="O70" s="24">
-        <v>49.936</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="O70" s="24"/>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A71" t="s">
-        <v>25</v>
-      </c>
-      <c r="B71">
+      <c r="A71" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="B71" s="13">
         <v>2019</v>
       </c>
       <c r="C71" s="2">
-        <v>43800</v>
-      </c>
-      <c r="D71" t="s">
+        <v>43814</v>
+      </c>
+      <c r="D71" s="13" t="s">
         <v>14</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="H71" s="3">
-        <v>27.4</v>
+        <v>25.246575342465754</v>
       </c>
       <c r="I71" s="3">
-        <v>31.512328767123286</v>
+        <v>28.024657534246575</v>
       </c>
       <c r="J71" s="6">
         <v>1</v>
       </c>
       <c r="K71">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L71">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="M71">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N71">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="O71" s="24">
-        <v>40.737000000000002</v>
+        <v>48.262</v>
       </c>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A72" t="s">
-        <v>25</v>
-      </c>
-      <c r="B72">
+      <c r="A72" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="B72" s="13">
         <v>2019</v>
       </c>
       <c r="C72" s="2">
-        <v>43800</v>
-      </c>
-      <c r="D72" t="s">
+        <v>43814</v>
+      </c>
+      <c r="D72" s="13" t="s">
         <v>14</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>124</v>
+        <v>78</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>121</v>
+        <v>96</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H72" s="3">
-        <v>20.238356164383561</v>
+        <v>20.934246575342467</v>
       </c>
       <c r="I72" s="3">
-        <v>23.12876712328767</v>
+        <v>19.898630136986302</v>
       </c>
       <c r="J72" s="6">
         <v>2</v>
       </c>
       <c r="K72">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L72">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M72">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N72">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="O72" s="24">
-        <v>40.737000000000002</v>
+        <v>48.262</v>
       </c>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A73" t="s">
-        <v>25</v>
-      </c>
-      <c r="B73">
+      <c r="A73" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="B73" s="13">
         <v>2019</v>
       </c>
       <c r="C73" s="2">
-        <v>43800</v>
-      </c>
-      <c r="D73" t="s">
+        <v>43814</v>
+      </c>
+      <c r="D73" s="13" t="s">
         <v>14</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>54</v>
+        <v>118</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>53</v>
+        <v>119</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="H73" s="3">
-        <v>18.93972602739726</v>
+        <v>27.361643835616437</v>
       </c>
       <c r="I73" s="3">
-        <v>20.449315068493149</v>
+        <v>33.095890410958901</v>
       </c>
       <c r="J73" s="6">
         <v>3</v>
       </c>
       <c r="K73">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L73">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M73">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N73">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="O73" s="24">
-        <v>40.737000000000002</v>
+        <v>48.262</v>
       </c>
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A74" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="B74" s="7">
+      <c r="A74" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B74" s="13">
         <v>2019</v>
       </c>
-      <c r="C74" s="8">
-        <v>43777</v>
-      </c>
-      <c r="D74" s="7" t="s">
+      <c r="C74" s="2">
+        <v>43807</v>
+      </c>
+      <c r="D74" s="13" t="s">
         <v>14</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>117</v>
+        <v>76</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G74" s="5" t="s">
         <v>42</v>
       </c>
       <c r="H74" s="3">
-        <v>27.931506849315067</v>
+        <v>25.227397260273971</v>
       </c>
       <c r="I74" s="3">
-        <v>25.153424657534245</v>
+        <v>23.789041095890411</v>
       </c>
       <c r="J74" s="6">
         <v>1</v>
@@ -4546,45 +4585,45 @@
         <v>0</v>
       </c>
       <c r="L74">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M74">
         <v>6</v>
       </c>
       <c r="N74">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="O74" s="24">
-        <v>52.779000000000003</v>
+        <v>49.936</v>
       </c>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A75" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="B75" s="7">
+      <c r="A75" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B75" s="13">
         <v>2019</v>
       </c>
-      <c r="C75" s="8">
-        <v>43777</v>
-      </c>
-      <c r="D75" s="7" t="s">
+      <c r="C75" s="2">
+        <v>43807</v>
+      </c>
+      <c r="D75" s="13" t="s">
         <v>14</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>50</v>
+        <v>97</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>63</v>
+        <v>120</v>
       </c>
       <c r="G75" s="5" t="s">
-        <v>28</v>
+        <v>99</v>
       </c>
       <c r="H75" s="3">
-        <v>25.682191780821917</v>
+        <v>22.931506849315067</v>
       </c>
       <c r="I75" s="3">
-        <v>25.19178082191781</v>
+        <v>23.55890410958904</v>
       </c>
       <c r="J75" s="6">
         <v>2</v>
@@ -4593,45 +4632,45 @@
         <v>0</v>
       </c>
       <c r="L75">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="M75">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N75">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O75" s="24">
-        <v>52.779000000000003</v>
+        <v>49.936</v>
       </c>
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A76" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="B76" s="7">
+      <c r="A76" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B76" s="13">
         <v>2019</v>
       </c>
-      <c r="C76" s="8">
-        <v>43777</v>
-      </c>
-      <c r="D76" s="7" t="s">
+      <c r="C76" s="2">
+        <v>43807</v>
+      </c>
+      <c r="D76" s="13" t="s">
         <v>14</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="F76" s="5" t="s">
-        <v>94</v>
+        <v>121</v>
       </c>
       <c r="G76" s="5" t="s">
-        <v>15</v>
+        <v>122</v>
       </c>
       <c r="H76" s="3">
-        <v>37.095890410958901</v>
+        <v>21.687671232876713</v>
       </c>
       <c r="I76" s="3">
-        <v>28.463013698630139</v>
+        <v>23.147945205479452</v>
       </c>
       <c r="J76" s="6">
         <v>3</v>
@@ -4640,186 +4679,186 @@
         <v>0</v>
       </c>
       <c r="L76">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N76">
         <v>19</v>
       </c>
       <c r="O76" s="24">
-        <v>52.779000000000003</v>
+        <v>49.936</v>
       </c>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A77" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="B77" s="13">
+      <c r="A77" t="s">
+        <v>25</v>
+      </c>
+      <c r="B77">
         <v>2019</v>
       </c>
       <c r="C77" s="2">
-        <v>43772</v>
-      </c>
-      <c r="D77" s="13" t="s">
+        <v>43800</v>
+      </c>
+      <c r="D77" t="s">
         <v>14</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>95</v>
+        <v>61</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>94</v>
+        <v>123</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H77" s="3">
-        <v>37.073972602739723</v>
+        <v>27.4</v>
       </c>
       <c r="I77" s="3">
-        <v>28.44109589041096</v>
+        <v>31.512328767123286</v>
       </c>
       <c r="J77" s="6">
         <v>1</v>
       </c>
       <c r="K77">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="L77">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M77">
         <v>3</v>
       </c>
       <c r="N77">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="O77" s="24">
-        <v>53.268000000000001</v>
+        <v>40.737000000000002</v>
       </c>
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A78" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="B78" s="13">
+      <c r="A78" t="s">
+        <v>25</v>
+      </c>
+      <c r="B78">
         <v>2019</v>
       </c>
       <c r="C78" s="2">
-        <v>43772</v>
-      </c>
-      <c r="D78" s="13" t="s">
+        <v>43800</v>
+      </c>
+      <c r="D78" t="s">
         <v>14</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H78" s="3">
-        <v>27.542465753424658</v>
+        <v>20.238356164383561</v>
       </c>
       <c r="I78" s="3">
-        <v>22.991780821917807</v>
+        <v>23.12876712328767</v>
       </c>
       <c r="J78" s="6">
         <v>2</v>
       </c>
       <c r="K78">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="L78">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M78">
         <v>3</v>
       </c>
       <c r="N78">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="O78" s="24">
-        <v>53.268000000000001</v>
+        <v>40.737000000000002</v>
       </c>
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A79" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="B79" s="13">
+      <c r="A79" t="s">
+        <v>25</v>
+      </c>
+      <c r="B79">
         <v>2019</v>
       </c>
       <c r="C79" s="2">
-        <v>43772</v>
-      </c>
-      <c r="D79" s="13" t="s">
+        <v>43800</v>
+      </c>
+      <c r="D79" t="s">
         <v>14</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>78</v>
+        <v>54</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>126</v>
+        <v>53</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H79" s="3">
-        <v>20.81917808219178</v>
+        <v>18.93972602739726</v>
       </c>
       <c r="I79" s="3">
-        <v>19.783561643835615</v>
+        <v>20.449315068493149</v>
       </c>
       <c r="J79" s="6">
         <v>3</v>
       </c>
       <c r="K79">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="L79">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M79">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N79">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="O79" s="24">
-        <v>53.268000000000001</v>
+        <v>40.737000000000002</v>
       </c>
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A80" t="s">
-        <v>45</v>
-      </c>
-      <c r="B80" s="13">
+      <c r="A80" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B80" s="7">
         <v>2019</v>
       </c>
-      <c r="C80" s="2">
-        <v>43527</v>
-      </c>
-      <c r="D80" s="13" t="s">
-        <v>18</v>
+      <c r="C80" s="8">
+        <v>43777</v>
+      </c>
+      <c r="D80" s="7" t="s">
+        <v>14</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G80" s="5" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="H80" s="3">
-        <v>36.402739726027399</v>
+        <v>27.931506849315067</v>
       </c>
       <c r="I80" s="3">
-        <v>27.769863013698629</v>
+        <v>25.153424657534245</v>
       </c>
       <c r="J80" s="6">
         <v>1</v>
@@ -4831,42 +4870,42 @@
         <v>9</v>
       </c>
       <c r="M80">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N80">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="O80" s="24">
-        <v>42.21</v>
+        <v>52.779000000000003</v>
       </c>
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A81" t="s">
-        <v>45</v>
-      </c>
-      <c r="B81" s="13">
+      <c r="A81" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B81" s="7">
         <v>2019</v>
       </c>
-      <c r="C81" s="2">
-        <v>43527</v>
-      </c>
-      <c r="D81" s="13" t="s">
-        <v>18</v>
+      <c r="C81" s="8">
+        <v>43777</v>
+      </c>
+      <c r="D81" s="7" t="s">
+        <v>14</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>127</v>
+        <v>63</v>
       </c>
       <c r="G81" s="5" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="H81" s="3">
-        <v>24.460273972602739</v>
+        <v>25.682191780821917</v>
       </c>
       <c r="I81" s="3">
-        <v>26.183561643835617</v>
+        <v>25.19178082191781</v>
       </c>
       <c r="J81" s="6">
         <v>2</v>
@@ -4875,45 +4914,45 @@
         <v>0</v>
       </c>
       <c r="L81">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M81">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N81">
         <v>31</v>
       </c>
       <c r="O81" s="24">
-        <v>42.21</v>
+        <v>52.779000000000003</v>
       </c>
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A82" t="s">
-        <v>45</v>
-      </c>
-      <c r="B82" s="13">
+      <c r="A82" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B82" s="7">
         <v>2019</v>
       </c>
-      <c r="C82" s="2">
-        <v>43527</v>
-      </c>
-      <c r="D82" s="13" t="s">
-        <v>18</v>
+      <c r="C82" s="8">
+        <v>43777</v>
+      </c>
+      <c r="D82" s="7" t="s">
+        <v>14</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>61</v>
+        <v>94</v>
       </c>
       <c r="G82" s="5" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H82" s="3">
-        <v>22.786301369863015</v>
+        <v>37.095890410958901</v>
       </c>
       <c r="I82" s="3">
-        <v>26.652054794520549</v>
+        <v>28.463013698630139</v>
       </c>
       <c r="J82" s="6">
         <v>3</v>
@@ -4922,27 +4961,27 @@
         <v>0</v>
       </c>
       <c r="L82">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M82">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N82">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="O82" s="24">
-        <v>42.21</v>
+        <v>52.779000000000003</v>
       </c>
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A83" t="s">
-        <v>25</v>
+      <c r="A83" s="13" t="s">
+        <v>44</v>
       </c>
       <c r="B83" s="13">
         <v>2019</v>
       </c>
       <c r="C83" s="2">
-        <v>43492</v>
+        <v>43772</v>
       </c>
       <c r="D83" s="13" t="s">
         <v>14</v>
@@ -4957,196 +4996,502 @@
         <v>15</v>
       </c>
       <c r="H83" s="3">
-        <v>36.30684931506849</v>
+        <v>37.073972602739723</v>
       </c>
       <c r="I83" s="3">
-        <v>27.673972602739727</v>
+        <v>28.44109589041096</v>
       </c>
       <c r="J83" s="6">
         <v>1</v>
       </c>
       <c r="K83">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L83">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M83">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N83">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="O83" s="24">
-        <v>51.688000000000002</v>
+        <v>53.268000000000001</v>
       </c>
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A84" t="s">
-        <v>25</v>
+      <c r="A84" s="13" t="s">
+        <v>44</v>
       </c>
       <c r="B84" s="13">
         <v>2019</v>
       </c>
       <c r="C84" s="2">
-        <v>43492</v>
+        <v>43772</v>
       </c>
       <c r="D84" s="13" t="s">
         <v>14</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="H84" s="3">
-        <v>23.227397260273971</v>
+        <v>27.542465753424658</v>
       </c>
       <c r="I84" s="3">
-        <v>28.890410958904109</v>
+        <v>22.991780821917807</v>
       </c>
       <c r="J84" s="6">
         <v>2</v>
       </c>
       <c r="K84">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L84">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M84">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N84">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="O84" s="24">
-        <v>51.688000000000002</v>
+        <v>53.268000000000001</v>
       </c>
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A85" t="s">
-        <v>25</v>
+      <c r="A85" s="13" t="s">
+        <v>44</v>
       </c>
       <c r="B85" s="13">
         <v>2019</v>
       </c>
       <c r="C85" s="2">
-        <v>43492</v>
+        <v>43772</v>
       </c>
       <c r="D85" s="13" t="s">
         <v>14</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H85" s="3">
-        <v>20.926027397260274</v>
+        <v>20.81917808219178</v>
       </c>
       <c r="I85" s="3">
-        <v>25.843835616438355</v>
+        <v>19.783561643835615</v>
       </c>
       <c r="J85" s="6">
         <v>3</v>
       </c>
       <c r="K85">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L85">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M85">
         <v>1</v>
       </c>
       <c r="N85">
+        <v>35</v>
+      </c>
+      <c r="O85" s="24">
+        <v>53.268000000000001</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A86" t="s">
+        <v>45</v>
+      </c>
+      <c r="B86" s="13">
+        <v>2019</v>
+      </c>
+      <c r="C86" s="2">
+        <v>43527</v>
+      </c>
+      <c r="D86" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="E86" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="F86" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G86" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H86" s="3">
+        <v>36.402739726027399</v>
+      </c>
+      <c r="I86" s="3">
+        <v>27.769863013698629</v>
+      </c>
+      <c r="J86" s="6">
+        <v>1</v>
+      </c>
+      <c r="K86">
+        <v>0</v>
+      </c>
+      <c r="L86">
+        <v>9</v>
+      </c>
+      <c r="M86">
+        <v>3</v>
+      </c>
+      <c r="N86">
+        <v>33</v>
+      </c>
+      <c r="O86" s="24">
+        <v>42.21</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A87" t="s">
+        <v>45</v>
+      </c>
+      <c r="B87" s="13">
+        <v>2019</v>
+      </c>
+      <c r="C87" s="2">
+        <v>43527</v>
+      </c>
+      <c r="D87" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="E87" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="F87" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="G87" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="H87" s="3">
+        <v>24.460273972602739</v>
+      </c>
+      <c r="I87" s="3">
+        <v>26.183561643835617</v>
+      </c>
+      <c r="J87" s="6">
+        <v>2</v>
+      </c>
+      <c r="K87">
+        <v>0</v>
+      </c>
+      <c r="L87">
+        <v>9</v>
+      </c>
+      <c r="M87">
+        <v>4</v>
+      </c>
+      <c r="N87">
+        <v>31</v>
+      </c>
+      <c r="O87" s="24">
+        <v>42.21</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A88" t="s">
+        <v>45</v>
+      </c>
+      <c r="B88" s="13">
+        <v>2019</v>
+      </c>
+      <c r="C88" s="2">
+        <v>43527</v>
+      </c>
+      <c r="D88" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="E88" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F88" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="G88" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H88" s="3">
+        <v>22.786301369863015</v>
+      </c>
+      <c r="I88" s="3">
+        <v>26.652054794520549</v>
+      </c>
+      <c r="J88" s="6">
+        <v>3</v>
+      </c>
+      <c r="K88">
+        <v>0</v>
+      </c>
+      <c r="L88">
+        <v>6</v>
+      </c>
+      <c r="M88">
+        <v>2</v>
+      </c>
+      <c r="N88">
+        <v>24</v>
+      </c>
+      <c r="O88" s="24">
+        <v>42.21</v>
+      </c>
+    </row>
+    <row r="89" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A89" t="s">
+        <v>25</v>
+      </c>
+      <c r="B89" s="13">
+        <v>2019</v>
+      </c>
+      <c r="C89" s="2">
+        <v>43492</v>
+      </c>
+      <c r="D89" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="G89" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H89" s="3">
+        <v>36.30684931506849</v>
+      </c>
+      <c r="I89" s="3">
+        <v>27.673972602739727</v>
+      </c>
+      <c r="J89" s="6">
+        <v>1</v>
+      </c>
+      <c r="K89">
+        <v>0</v>
+      </c>
+      <c r="L89">
+        <v>7</v>
+      </c>
+      <c r="M89">
+        <v>4</v>
+      </c>
+      <c r="N89">
+        <v>29</v>
+      </c>
+      <c r="O89" s="24">
+        <v>51.688000000000002</v>
+      </c>
+    </row>
+    <row r="90" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A90" t="s">
+        <v>25</v>
+      </c>
+      <c r="B90" s="13">
+        <v>2019</v>
+      </c>
+      <c r="C90" s="2">
+        <v>43492</v>
+      </c>
+      <c r="D90" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G90" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H90" s="3">
+        <v>23.227397260273971</v>
+      </c>
+      <c r="I90" s="3">
+        <v>28.890410958904109</v>
+      </c>
+      <c r="J90" s="6">
+        <v>2</v>
+      </c>
+      <c r="K90">
+        <v>0</v>
+      </c>
+      <c r="L90">
+        <v>8</v>
+      </c>
+      <c r="M90">
+        <v>1</v>
+      </c>
+      <c r="N90">
+        <v>24</v>
+      </c>
+      <c r="O90" s="24">
+        <v>51.688000000000002</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A91" t="s">
+        <v>25</v>
+      </c>
+      <c r="B91" s="13">
+        <v>2019</v>
+      </c>
+      <c r="C91" s="2">
+        <v>43492</v>
+      </c>
+      <c r="D91" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="G91" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H91" s="3">
+        <v>20.926027397260274</v>
+      </c>
+      <c r="I91" s="3">
+        <v>25.843835616438355</v>
+      </c>
+      <c r="J91" s="6">
+        <v>3</v>
+      </c>
+      <c r="K91">
+        <v>0</v>
+      </c>
+      <c r="L91">
+        <v>4</v>
+      </c>
+      <c r="M91">
+        <v>1</v>
+      </c>
+      <c r="N91">
         <v>12</v>
       </c>
-      <c r="O85" s="24">
+      <c r="O91" s="24">
         <v>51.688000000000002</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O85" xr:uid="{856B23EE-F0D3-4856-AD89-ACB67D64024E}"/>
-  <conditionalFormatting sqref="A74:D76 A77:B79 D77:D79">
-    <cfRule type="expression" dxfId="16" priority="36">
+  <autoFilter ref="A1:O91" xr:uid="{856B23EE-F0D3-4856-AD89-ACB67D64024E}"/>
+  <conditionalFormatting sqref="A80:D82 A83:B85 D83:D85">
+    <cfRule type="expression" dxfId="20" priority="40">
       <formula>#REF!="F"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="15" priority="37">
+    <cfRule type="expression" dxfId="19" priority="41">
       <formula>#REF!="Q"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="38">
+    <cfRule type="expression" dxfId="18" priority="42">
       <formula>#REF!="R1"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A80:D82 A83:B85 D83:D85">
-    <cfRule type="expression" dxfId="13" priority="45">
+  <conditionalFormatting sqref="A86:D88 A89:B91 D89:D91">
+    <cfRule type="expression" dxfId="17" priority="49">
       <formula>#REF!="F"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="46">
+    <cfRule type="expression" dxfId="16" priority="50">
       <formula>#REF!="Q"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H5:I85 A53:D55 A56:B58 D56:D58">
-    <cfRule type="expression" dxfId="11" priority="16">
+  <conditionalFormatting sqref="H11:I91 A59:D61 A62:B64 D62:D64">
+    <cfRule type="expression" dxfId="15" priority="20">
       <formula>#REF!="R1"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="17">
+    <cfRule type="expression" dxfId="14" priority="21">
       <formula>#REF!="F"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="18">
+    <cfRule type="expression" dxfId="13" priority="22">
       <formula>#REF!="Q"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J65">
-    <cfRule type="cellIs" dxfId="8" priority="1" operator="between">
+  <conditionalFormatting sqref="J8:J71">
+    <cfRule type="cellIs" dxfId="12" priority="5" operator="between">
       <formula>0</formula>
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K68:K70">
-    <cfRule type="cellIs" dxfId="7" priority="19" operator="between">
+  <conditionalFormatting sqref="K74:K76">
+    <cfRule type="cellIs" dxfId="11" priority="23" operator="between">
       <formula>1</formula>
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="20" operator="between">
+    <cfRule type="cellIs" dxfId="10" priority="24" operator="between">
       <formula>2</formula>
       <formula>2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="21" operator="between">
+    <cfRule type="cellIs" dxfId="9" priority="25" operator="between">
       <formula>3</formula>
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="22" operator="between">
+    <cfRule type="cellIs" dxfId="8" priority="26" operator="between">
       <formula>5</formula>
       <formula>5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N68:N70">
-    <cfRule type="cellIs" dxfId="3" priority="23" operator="between">
+  <conditionalFormatting sqref="N74:N76">
+    <cfRule type="cellIs" dxfId="7" priority="27" operator="between">
       <formula>2</formula>
       <formula>2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="24" operator="between">
+    <cfRule type="cellIs" dxfId="6" priority="28" operator="between">
       <formula>4</formula>
       <formula>4</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="25" operator="between">
+    <cfRule type="cellIs" dxfId="5" priority="29" operator="between">
       <formula>6</formula>
       <formula>6</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="26" operator="between">
+    <cfRule type="cellIs" dxfId="4" priority="30" operator="between">
       <formula>10</formula>
       <formula>10</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J4">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="between">
+      <formula>0</formula>
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2:K4">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="between">
+      <formula>0</formula>
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J5:J7">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="between">
+      <formula>0</formula>
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K5:K7">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="between">
+      <formula>0</formula>
+      <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
